--- a/Data/LREROBOT/Rapport.xlsx
+++ b/Data/LREROBOT/Rapport.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
-  <x:workbookPr codeName="ThisWorkbook"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15">
+  <x:fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <x:workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walid ABRA\Documents\UiPath\PerformerProjet1LRE\Data\LREROBOT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpa.lre.res.dev\Documents\UiPath\PerformerProjet1LRE\Data\LREROBOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33908696-274E-497B-8AFC-21411C96981B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
-    <x:workbookView xWindow="9360" yWindow="4350" windowWidth="38700" windowHeight="15225" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <x:workbookView xWindow="9360" yWindow="4350" windowWidth="38700" windowHeight="15225" firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Rapport" sheetId="2" r:id="rId1"/>
@@ -50,2044 +49,1639 @@
     <x:t>Sous Dossier</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-0b7627d7-1d6c-48dc-a965-1603668c1f7e-6eca2e86d4b64bfa97c93d76258c490b.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001325_MATMUTRPA_000000002.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\dossier inexistant - clef soc KO.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144248_MATMUTRPA_000000001.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
+    <x:t>Fail</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE014 - [120000492449K | la clé extraite K   est différente de la clé générée Q] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Non</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\7766679772</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144255_MATMUTRPA_000000002.pdf</x:t>
+  </x:si>
+  <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
-    <x:t>Success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Non</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-1d9a65fc-32da-4966-be02-6b245853558d-b157206dacea4b17ab283f53537ab3e1.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001330_MATMUTRPA_000000003.pdf</x:t>
+    <x:t>BE014 - [840509002599L | la clé extraite L   est différente de la clé générée Y] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Oui</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\9432160377</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144256_MATMUTRPA_000000003.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>3</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-261d2106-86b9-4286-b8a0-f541dee4c1ff-8c2abf9cbf8b4db1bcd12869c630e227.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001330_MATMUTRPA_000000004.pdf</x:t>
+    <x:t>BE014 - [980000809205Y | la clé extraite Y   est différente de la clé générée C] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\9016932803</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144257_MATMUTRPA_000000004.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>4</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-2e4acd3c-dcac-4447-a896-9788960fc9df-fb64965082e642cc903dfdb7c2a2b7e9.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001331_MATMUTRPA_000000005.pdf</x:t>
+    <x:t>BE014 - [980002669133E | la clé extraite E   est différente de la clé générée J] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144259_MATMUTRPA_000000005.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>5</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-34b69bf6-22b6-442f-99dc-4d540821382f-c3f8f010af6442e08314016013b3943c.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001331_MATMUTRPA_000000006.pdf</x:t>
+    <x:t>BE014 - [980001601482V | la clé extraite V   est différente de la clé générée H] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144300_MATMUTRPA_000000005.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE014 - [980000996047P | la clé extraite P   est différente de la clé générée T] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE014 - [980002231588C | la clé extraite C   est différente de la clé générée A] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144301_MATMUTRPA_000000005.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE014 - [980002319455U | la clé extraite U   est différente de la clé générée G] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE014 - [500204000580R | la clé extraite R   est différente de la clé générée V] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144302_MATMUTRPA_000000005.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE014 - [980002584346K | la clé extraite K   est différente de la clé générée X] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE012 - [Santé] Hors périmètre</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE014 - [980002867805b | la clé extraite b   est différente de la clé générée P] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-0b7627d7-1d6c-48dc-a965-1603668c1f7e-6eca2e86d4b64bfa97c93d76258c490b.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144303_MATMUTRPA_000000006.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>6</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-41caba1f-9585-4ad9-bc8c-2b61ddb11ba8-b80fd010cd3f4434a24f2ca9a13388cc.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001332_MATMUTRPA_000000007.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-2e4acd3c-dcac-4447-a896-9788960fc9df-fb64965082e642cc903dfdb7c2a2b7e9.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144304_MATMUTRPA_000000007.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-538222e7-c391-4f5c-98f0-6094bc3e36e3-ae680ebeafa5462b9cbcf0c9ef369277.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001332_MATMUTRPA_000000008.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-5adf900c-5bbd-489c-8f17-3203c28bceb4-499f2e67f9f941149c4134b435eb568b.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144304_MATMUTRPA_000000008.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>8</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-5adf900c-5bbd-489c-8f17-3203c28bceb4-499f2e67f9f941149c4134b435eb568b.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001333_MATMUTRPA_000000009.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250805_133800_MATMUTRPA_000000001.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144305_MATMUTRPA_000000009.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>9</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-60254d47-6f17-48b4-bcc8-3ad2476c97db-57c26eeaf22243469a754ad823ae05e3.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001333_MATMUTRPA_000000010.pdf</x:t>
+    <x:t>BE014 - [980000162834M | la clé extraite M   est différente de la clé générée Z] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\dossier inexistant - clef soc KO - 2.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144306_MATMUTRPA_000000010.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>10</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-72905918-5d9e-4902-a217-3b3578d318ee-d53f87443b474ce696c632ba10cd01f1.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001334_MATMUTRPA_000000011.pdf</x:t>
+    <x:t>BE014 - [240002548934U | la clé extraite U   est différente de la clé générée V] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-261d2106-86b9-4286-b8a0-f541dee4c1ff-8c2abf9cbf8b4db1bcd12869c630e227.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144306_MATMUTRPA_000000011.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>11</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-9bd39f23-ba73-47d0-8d83-600d67ebde8d-06b197c719a24fecb8a69e6a48286abe.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001334_MATMUTRPA_000000012.pdf</x:t>
+    <x:t>BE014 - [980003668206N | la clé extraite N   est différente de la clé générée S] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-34b69bf6-22b6-442f-99dc-4d540821382f-c3f8f010af6442e08314016013b3943c.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144307_MATMUTRPA_000000012.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>12</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-9e7f26ff-6a64-42ed-a3f4-6d4d1927ecc0-2d3294623f924ec4ab82ce1a20b8ca3f.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001335_MATMUTRPA_000000013.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-41caba1f-9585-4ad9-bc8c-2b61ddb11ba8-b80fd010cd3f4434a24f2ca9a13388cc.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144308_MATMUTRPA_000000013.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>13</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-b9e9838b-54f3-490f-8706-ab0cecfd4a8d-70c4b9c25e01420f9eccbf4cb349d568.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001335_MATMUTRPA_000000014.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-538222e7-c391-4f5c-98f0-6094bc3e36e3-ae680ebeafa5462b9cbcf0c9ef369277.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144308_MATMUTRPA_000000014.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>14</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-bc75719f-0e52-43a6-8953-6f0ef0959427-df70e4692e5b4f6c82f965461fc63970.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001336_MATMUTRPA_000000015.pdf</x:t>
+    <x:t>BE014 - [960001101990Q | la clé extraite Q   est différente de la clé générée U] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-60254d47-6f17-48b4-bcc8-3ad2476c97db-57c26eeaf22243469a754ad823ae05e3.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144309_MATMUTRPA_000000015.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>15</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-d7b5dbf5-25c6-4131-9f4d-1d6e0c2fa058-d473d2a755dc43bba591baaca70ff1bb.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001336_MATMUTRPA_000000016.pdf</x:t>
+    <x:t>BE014 - [830409004820P | la clé extraite P   est différente de la clé générée T] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-72905918-5d9e-4902-a217-3b3578d318ee-d53f87443b474ce696c632ba10cd01f1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144310_MATMUTRPA_000000016.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>16</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-f0fdaf5b-420d-469a-a394-3b9e9993da20-82cbc868c06f4965bdf49cdb776af571.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001337_MATMUTRPA_000000017.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-9e7f26ff-6a64-42ed-a3f4-6d4d1927ecc0-2d3294623f924ec4ab82ce1a20b8ca3f.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144310_MATMUTRPA_000000017.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>17</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\14596-11380402-NOTIF-2024-11-22-13100402-fbedc888-178a-4175-8126-629b4883f304-82c7244800fe4ebea415e06ea86af128.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001337_MATMUTRPA_000000018.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-a7a283b3-12ed-461f-a410-da38109fe432-b5cf3950094b49e7aa6654cd5b505c97.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144311_MATMUTRPA_000000018.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>18</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235520_MATMUTRPA_000000001.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001338_MATMUTRPA_000000019.pdf</x:t>
+    <x:t>BE011 -Extraction KO/format KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-b9e9838b-54f3-490f-8706-ab0cecfd4a8d-70c4b9c25e01420f9eccbf4cb349d568.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144312_MATMUTRPA_000000019.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>19</x:t>
   </x:si>
   <x:si>
-    <x:t>Fail</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE011 -BE011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235521_MATMUTRPA_000000002.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001338_MATMUTRPA_000000020.pdf</x:t>
+    <x:t>BE014 - [980000802716M | la clé extraite M   est différente de la clé générée Z] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-bc75719f-0e52-43a6-8953-6f0ef0959427-df70e4692e5b4f6c82f965461fc63970.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144312_MATMUTRPA_000000020.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>20</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235521_MATMUTRPA_000000003.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001339_MATMUTRPA_000000021.pdf</x:t>
+    <x:t>BE014 - [800370709095F | la clé extraite F   est différente de la clé générée D] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-d7b5dbf5-25c6-4131-9f4d-1d6e0c2fa058-d473d2a755dc43bba591baaca70ff1bb.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144313_MATMUTRPA_000000021.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>21</x:t>
   </x:si>
   <x:si>
-    <x:t>BE012 - BE012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235522_MATMUTRPA_000000004.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001339_MATMUTRPA_000000022.pdf</x:t>
+    <x:t>BE014 - [980002691729L | la clé extraite L   est différente de la clé générée Y] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-f0fdaf5b-420d-469a-a394-3b9e9993da20-82cbc868c06f4965bdf49cdb776af571.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144314_MATMUTRPA_000000022.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>22</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235522_MATMUTRPA_000000005.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001340_MATMUTRPA_000000023.pdf</x:t>
+    <x:t>BE014 - [740109006318S | la clé extraite S   est différente de la clé générée E] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-fbedc888-178a-4175-8126-629b4883f304-82c7244800fe4ebea415e06ea86af128.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144314_MATMUTRPA_000000023.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>23</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235523_MATMUTRPA_000000006.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001341_MATMUTRPA_000000024.pdf</x:t>
+    <x:t>BE014 - [450209002215X | la clé extraite X   est différente de la clé générée B] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150241_MATMUTRPA_000000001.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144315_MATMUTRPA_000000024.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>24</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235524_MATMUTRPA_000000007.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001341_MATMUTRPA_000000025.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150305_MATMUTRPA_000000003.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144316_MATMUTRPA_000000025.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>25</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235524_MATMUTRPA_000000008.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001342_MATMUTRPA_000000026.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150311_MATMUTRPA_000000009.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144317_MATMUTRPA_000000026.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>26</x:t>
   </x:si>
   <x:si>
-    <x:t>BE012 - 980003347476Q| BE012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235525_MATMUTRPA_000000009.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001343_MATMUTRPA_000000027.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150314_MATMUTRPA_000000014.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144318_MATMUTRPA_000000027.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>27</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235526_MATMUTRPA_000000010.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001343_MATMUTRPA_000000028.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150316_MATMUTRPA_000000016.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144318_MATMUTRPA_000000028.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>28</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235526_MATMUTRPA_000000011.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001344_MATMUTRPA_000000029.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\28284-12900402-NOTIF-2024-11-22-13100402-461b2d82-cec6-422e-9477-92fe7c106dbe-a4b2eb3440a240538dc2c7c9dab6d27f.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144319_MATMUTRPA_000000029.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>29</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235527_MATMUTRPA_000000012.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001344_MATMUTRPA_000000030.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\28284-12900402-NOTIF-2024-11-22-13100402-be8b2fde-eaa7-4fef-9c86-f9cf394a9158-f05448874c204e8f97c5021cace221e9.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144320_MATMUTRPA_000000030.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>30</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235527_MATMUTRPA_000000013.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001345_MATMUTRPA_000000031.pdf</x:t>
+    <x:t>BE014 - [980002163671G | la clé extraite G   est différente de la clé générée L] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\40763-04550404-NOTIF-2024-11-22-13100402-17c8e4dd-5ea3-4b7d-b981-ce1fc8701fe5-626f4115dcfd47e5bb8684b4302becbc.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144321_MATMUTRPA_000000031.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>31</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235528_MATMUTRPA_000000014.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001346_MATMUTRPA_000000032.pdf</x:t>
+    <x:t>BE014 - [980001360786F | la clé extraite F   est différente de la clé générée K] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\40763-04550404-NOTIF-2024-11-22-13100402-398ccc85-4870-4ac2-a681-2341e8942eec-acdc01e31a644e0897669be1340a2bed.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144321_MATMUTRPA_000000032.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>32</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235528_MATMUTRPA_000000015.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001346_MATMUTRPA_000000033.pdf</x:t>
+    <x:t>BE014 - [980003284391H | la clé extraite H   est différente de la clé générée M] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T135427.629.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144322_MATMUTRPA_000000033.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>33</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235529_MATMUTRPA_000000016.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001347_MATMUTRPA_000000034.pdf</x:t>
+    <x:t>BE014 - [960000651112N | la clé extraite N   est différente de la clé générée S] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T135602.938.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144323_MATMUTRPA_000000034.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>34</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235529_MATMUTRPA_000000017.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001347_MATMUTRPA_000000035.pdf</x:t>
+    <x:t>BE014 - [759100003262F | la clé extraite F   est différente de la clé générée K] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T135729.486.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144323_MATMUTRPA_000000035.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>35</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235529_MATMUTRPA_000000018.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001348_MATMUTRPA_000000036.pdf</x:t>
+    <x:t>BE014 - [980002699086A | la clé extraite A   est différente de la clé générée P] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140113.150.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144324_MATMUTRPA_000000036.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>36</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235530_MATMUTRPA_000000019.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001348_MATMUTRPA_000000037.pdf</x:t>
+    <x:t>BE014 - [980000549752F | la clé extraite F   est différente de la clé générée K] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140229.156.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144325_MATMUTRPA_000000037.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>37</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235530_MATMUTRPA_000000020.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001349_MATMUTRPA_000000038.pdf</x:t>
+    <x:t>BE014 - [980003532138D | la clé extraite D   est différente de la clé générée R] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140312.416.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144326_MATMUTRPA_000000038.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>38</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235531_MATMUTRPA_000000021.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001349_MATMUTRPA_000000039.pdf</x:t>
+    <x:t>BE014 - [980002834151M | la clé extraite M   est différente de la clé générée Z] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140407.802.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144327_MATMUTRPA_000000039.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>39</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235531_MATMUTRPA_000000022.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001350_MATMUTRPA_000000040.pdf</x:t>
+    <x:t>BE014 - [980002570501k | la clé extraite k   est différente de la clé générée X] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140503.945.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144327_MATMUTRPA_000000040.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>40</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235532_MATMUTRPA_000000023.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001351_MATMUTRPA_000000041.pdf</x:t>
+    <x:t>BE014 - [980002286686F | la clé extraite F   est différente de la clé générée K] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140554.081.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144328_MATMUTRPA_000000041.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>41</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235532_MATMUTRPA_000000024.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001351_MATMUTRPA_000000042.pdf</x:t>
+    <x:t>BE014 - [980001956663G | la clé extraite G   est différente de la clé générée L] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140635.034.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144329_MATMUTRPA_000000042.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>42</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235532_MATMUTRPA_000000025.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001352_MATMUTRPA_000000043.pdf</x:t>
+    <x:t>BE014 - [980002409304J | la clé extraite J   est différente de la clé générée W] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140722.293.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144330_MATMUTRPA_000000043.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>43</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235533_MATMUTRPA_000000026.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001353_MATMUTRPA_000000044.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140820.205.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144330_MATMUTRPA_000000044.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>44</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235533_MATMUTRPA_000000027.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001353_MATMUTRPA_000000045.pdf</x:t>
+    <x:t>BE014 - [980002022787B | la clé extraite B   est différente de la clé générée D] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140909.695.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144331_MATMUTRPA_000000045.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>45</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235534_MATMUTRPA_000000028.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001354_MATMUTRPA_000000046.pdf</x:t>
+    <x:t>BE014 - [570109000951N | la clé extraite N   est différente de la clé générée S] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140949.978.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144332_MATMUTRPA_000000046.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>46</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235534_MATMUTRPA_000000029.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001354_MATMUTRPA_000000047.pdf</x:t>
+    <x:t>BE014 - [980003174468T | la clé extraite T   est différente de la clé générée F] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141038.018.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144332_MATMUTRPA_000000047.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>47</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235534_MATMUTRPA_000000030.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001355_MATMUTRPA_000000048.pdf</x:t>
+    <x:t>BE014 - [980003511683Y | la clé extraite Y   est différente de la clé générée C] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141117.536.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144333_MATMUTRPA_000000048.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>48</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235535_MATMUTRPA_000000031.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001355_MATMUTRPA_000000049.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141207.446.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144334_MATMUTRPA_000000049.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>49</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235535_MATMUTRPA_000000032.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001356_MATMUTRPA_000000050.pdf</x:t>
+    <x:t>BE014 - [980002449095N | la clé extraite N   est différente de la clé générée S] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141322.570.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144334_MATMUTRPA_000000050.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>50</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235536_MATMUTRPA_000000033.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001357_MATMUTRPA_000000051.pdf</x:t>
+    <x:t>BE014 - [980003185070B | la clé extraite B   est différente de la clé générée D] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141417.553.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144335_MATMUTRPA_000000051.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>51</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235536_MATMUTRPA_000000034.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001357_MATMUTRPA_000000052.pdf</x:t>
+    <x:t>BE014 - [980002921162W | la clé extraite W   est différente de la clé générée A] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141514.019.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144336_MATMUTRPA_000000052.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>52</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235536_MATMUTRPA_000000035.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001358_MATMUTRPA_000000053.pdf</x:t>
+    <x:t>BE014 - [980000628327V | la clé extraite V   est différente de la clé générée H] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\1732366193</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144336_MATMUTRPA_000000053.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>53</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235537_MATMUTRPA_000000036.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001358_MATMUTRPA_000000054.pdf</x:t>
+    <x:t>BE014 - [980003891334Z | la clé extraite Z   est différente de la clé générée D] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\2281907752</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144337_MATMUTRPA_000000054.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>54</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235537_MATMUTRPA_000000037.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001359_MATMUTRPA_000000055.pdf</x:t>
+    <x:t>BE014 - [980003177319U | la clé extraite U   est différente de la clé générée G] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\2095807535</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144338_MATMUTRPA_000000055.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>55</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235538_MATMUTRPA_000000038.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001359_MATMUTRPA_000000056.pdf</x:t>
+    <x:t>BE014 - [980000864226P | la clé extraite P   est différente de la clé générée T] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\3332348086</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144339_MATMUTRPA_000000056.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>56</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235538_MATMUTRPA_000000039.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001400_MATMUTRPA_000000057.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\2037793408</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144340_MATMUTRPA_000000057.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>57</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235538_MATMUTRPA_000000040.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001401_MATMUTRPA_000000058.pdf</x:t>
+    <x:t>BE014 - [980002014599R | la clé extraite R   est différente de la clé générée V] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\1009512117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144341_MATMUTRPA_000000058.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>58</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235539_MATMUTRPA_000000041.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001406_MATMUTRPA_000000059.pdf</x:t>
+    <x:t>BE014 - [980002293007G | la clé extraite G   est différente de la clé générée L] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\6544809077</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144341_MATMUTRPA_000000059.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>59</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235539_MATMUTRPA_000000042.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001406_MATMUTRPA_000000060.pdf</x:t>
+    <x:t>BE014 - [510709001741F | la clé extraite F   est différente de la clé générée K] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\3045825747</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144342_MATMUTRPA_000000060.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>60</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235540_MATMUTRPA_000000043.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001407_MATMUTRPA_000000061.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\6364486263</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144343_MATMUTRPA_000000061.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>61</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235540_MATMUTRPA_000000044.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001407_MATMUTRPA_000000062.pdf</x:t>
+    <x:t>BE014 - [980000535994X | la clé extraite X   est différente de la clé générée B] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\6876400847</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144344_MATMUTRPA_000000062.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>62</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235540_MATMUTRPA_000000045.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001408_MATMUTRPA_000000063.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\1879992102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144345_MATMUTRPA_000000063.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>63</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235541_MATMUTRPA_000000046.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001408_MATMUTRPA_000000064.pdf</x:t>
+    <x:t>BE014 - [980002584766V | la clé extraite V   est différente de la clé générée H] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\5988929419</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144345_MATMUTRPA_000000064.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>64</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235541_MATMUTRPA_000000047.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001409_MATMUTRPA_000000065.pdf</x:t>
+    <x:t>BE014 - [980003084341H | la clé extraite H   est différente de la clé générée M] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\message_43310327_resiliation@matmut.fr.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144346_MATMUTRPA_000000065.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>65</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235542_MATMUTRPA_000000048.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001409_MATMUTRPA_000000066.pdf</x:t>
+    <x:t>BE014 - [980002057643U | la clé extraite U   est différente de la clé générée G] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\message_43310334_resiliation@matmut.fr.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144347_MATMUTRPA_000000066.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>66</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235542_MATMUTRPA_000000049.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001410_MATMUTRPA_000000067.pdf</x:t>
+    <x:t>BE014 - [980900224297k | la clé extraite k   est différente de la clé générée X] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\message_43310361_resiliation@matmut.fr.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144348_MATMUTRPA_000000067.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>67</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235542_MATMUTRPA_000000050.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001410_MATMUTRPA_000000068.pdf</x:t>
+    <x:t>BE014 - [980000771436D | la clé extraite D   est différente de la clé générée R] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\message_43310674_resiliation@matmut.fr.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144349_MATMUTRPA_000000068.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>68</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235543_MATMUTRPA_000000051.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001411_MATMUTRPA_000000069.pdf</x:t>
+    <x:t>BE014 - [980002150415V | la clé extraite V   est différente de la clé générée H] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\message_43335289_resiliation@matmut.fr.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144349_MATMUTRPA_000000069.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>69</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235543_MATMUTRPA_000000052.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001411_MATMUTRPA_000000070.pdf</x:t>
+    <x:t>BE014 - [980002484576Y | la clé extraite Y   est différente de la clé générée C] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\message_43379712_resiliation@matmut.fr.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144350_MATMUTRPA_000000070.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>70</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235544_MATMUTRPA_000000053.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001412_MATMUTRPA_000000071.pdf</x:t>
+    <x:t>BE014 - [980002049129S | la clé extraite S   est différente de la clé générée E] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\message_43425700_resiliation@matmut.fr.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144351_MATMUTRPA_000000071.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>71</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235544_MATMUTRPA_000000054.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001412_MATMUTRPA_000000072.pdf</x:t>
+    <x:t>BE014 - [980003306188Q | la clé extraite Q   est différente de la clé générée U] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-873846be-1a72-46f8-99b1-96a162f0e422.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144351_MATMUTRPA_000000072.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>72</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235544_MATMUTRPA_000000055.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001413_MATMUTRPA_000000073.pdf</x:t>
+    <x:t>BE014 - [750209007074H | la clé extraite H   est différente de la clé générée M] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-a4d7dc50-1859-42d5-8719-089e9b9dde71.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144352_MATMUTRPA_000000073.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>73</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235545_MATMUTRPA_000000056.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001414_MATMUTRPA_000000074.pdf</x:t>
+    <x:t>BE014 - [960000068849A | la clé extraite A   est différente de la clé générée P] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-a87518f5-6477-42a0-bebc-18c0f42df781.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144355_MATMUTRPA_000000074.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>74</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235545_MATMUTRPA_000000057.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001414_MATMUTRPA_000000075.pdf</x:t>
+    <x:t>BE014 - [560104002270X | la clé extraite X   est différente de la clé générée B] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-ba00efcc-5cf9-4fef-84f4-2014e001ec49.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144357_MATMUTRPA_000000075.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>75</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235546_MATMUTRPA_000000058.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001415_MATMUTRPA_000000076.pdf</x:t>
+    <x:t>BE014 - [980003033071M | la clé extraite M   est différente de la clé générée Z] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-cbb3e6bc-cf3e-4aa1-bc80-7e48c234e478.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144357_MATMUTRPA_000000076.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>76</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235546_MATMUTRPA_000000059.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001415_MATMUTRPA_000000077.pdf</x:t>
+    <x:t>BE014 - [980001503958D | la clé extraite D   est différente de la clé générée R] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-d81d8a6b-1e4c-4e63-b367-d9b8886c6d9a.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144358_MATMUTRPA_000000077.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>77</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235547_MATMUTRPA_000000060.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001416_MATMUTRPA_000000078.pdf</x:t>
+    <x:t>BE014 - [980000661440V | la clé extraite V   est différente de la clé générée H] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-d8d535d2-0678-41f4-815f-04dff1d2dd0c.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144359_MATMUTRPA_000000078.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>78</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235547_MATMUTRPA_000000061.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001416_MATMUTRPA_000000079.pdf</x:t>
+    <x:t>BE014 - [980002931617H | la clé extraite H   est différente de la clé générée M] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-dca5a1ab-31e9-47b8-8c86-d8e5f682607e.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144400_MATMUTRPA_000000079.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>79</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235547_MATMUTRPA_000000062.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001417_MATMUTRPA_000000080.pdf</x:t>
+    <x:t>BE014 - [960001328099R | la clé extraite R   est différente de la clé générée V] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-e4947664-09fe-4856-91fa-a54ffced7ee6.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144401_MATMUTRPA_000000080.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>80</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235548_MATMUTRPA_000000063.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001417_MATMUTRPA_000000081.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-e55206cb-5ecf-4568-9183-a280a60e41c1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144401_MATMUTRPA_000000081.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>81</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235548_MATMUTRPA_000000064.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001418_MATMUTRPA_000000082.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-eeb82fcb-dfb1-4b9a-9bff-e411581472ce.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144402_MATMUTRPA_000000082.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>82</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235548_MATMUTRPA_000000065.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001418_MATMUTRPA_000000083.pdf</x:t>
+    <x:t>BE014 - [352011314457M | la clé extraite M   est différente de la clé générée Z] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-f301cec9-984a-450e-b224-c563f5203433.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144403_MATMUTRPA_000000083.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>83</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235549_MATMUTRPA_000000066.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001419_MATMUTRPA_000000084.pdf</x:t>
+    <x:t>BE014 - [980900006190E | la clé extraite E   est différente de la clé générée J] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-02e06e81-c885-431d-a456-60ab127dc071.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144404_MATMUTRPA_000000084.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>84</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235549_MATMUTRPA_000000067.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001419_MATMUTRPA_000000085.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-0e0aea93-f361-4739-9ed7-cdb67803fd84.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144405_MATMUTRPA_000000085.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>85</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235550_MATMUTRPA_000000068.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001420_MATMUTRPA_000000086.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-1715cf71-724d-45b6-8e15-e86c557419a4.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144406_MATMUTRPA_000000086.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>86</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235550_MATMUTRPA_000000069.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001420_MATMUTRPA_000000087.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-1876f30c-83a4-4a4c-9c55-094fdf3ac844.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144406_MATMUTRPA_000000087.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>87</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235551_MATMUTRPA_000000070.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001421_MATMUTRPA_000000088.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-19c03249-bbfc-4c49-b058-3af16c158f0f.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144407_MATMUTRPA_000000088.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>88</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235551_MATMUTRPA_000000071.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001421_MATMUTRPA_000000089.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-1aeb8441-3356-4a2d-ba7c-d783f27dae69.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144408_MATMUTRPA_000000089.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>89</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235552_MATMUTRPA_000000072.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001422_MATMUTRPA_000000090.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-1c7cbc6f-6bb2-4b7b-9968-ca6bc78fe996.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144409_MATMUTRPA_000000090.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>90</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235552_MATMUTRPA_000000073.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001422_MATMUTRPA_000000091.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-23557855-7620-4ae5-9241-fcc4412132a8.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144409_MATMUTRPA_000000091.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>91</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235552_MATMUTRPA_000000074.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001423_MATMUTRPA_000000092.pdf</x:t>
+    <x:t>BE014 - [980003104385B | la clé extraite B   est différente de la clé générée D] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-23e9ee7b-1c83-4124-9a3b-1f8b9052a987.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144410_MATMUTRPA_000000092.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>92</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235553_MATMUTRPA_000000075.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001423_MATMUTRPA_000000093.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-338f2191-3f8d-4d87-9910-2483cf9753d1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144411_MATMUTRPA_000000093.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>93</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235554_MATMUTRPA_000000076.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001424_MATMUTRPA_000000094.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-38ca5ea7-46a9-422d-a449-10947af6f55a.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144412_MATMUTRPA_000000094.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>94</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235555_MATMUTRPA_000000077.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001424_MATMUTRPA_000000095.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-3c267d7a-d52b-4492-a732-7a3e45159f79.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144412_MATMUTRPA_000000095.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>95</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235555_MATMUTRPA_000000078.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001425_MATMUTRPA_000000096.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-3df6b24f-3c10-49d2-bef4-85d02d4d32c8.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144413_MATMUTRPA_000000096.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>96</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235556_MATMUTRPA_000000079.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001425_MATMUTRPA_000000097.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-40f6d100-df71-4cb6-b435-c92ee1b7a806.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144414_MATMUTRPA_000000097.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>97</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235556_MATMUTRPA_000000080.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001426_MATMUTRPA_000000098.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-43115be2-cca2-44d8-bb9c-2abec01bff83.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144414_MATMUTRPA_000000098.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>98</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235557_MATMUTRPA_000000081.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001426_MATMUTRPA_000000099.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-4ac8d681-6792-426f-a1d9-97439fdd85b0.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144415_MATMUTRPA_000000099.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>99</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235557_MATMUTRPA_000000082.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001427_MATMUTRPA_000000100.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-4f14000d-93a1-4515-80d8-b2647251b2e4.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144416_MATMUTRPA_000000100.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>100</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235557_MATMUTRPA_000000083.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001427_MATMUTRPA_000000101.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-50842b6b-c5bf-4c18-bc16-877c4c658790.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144417_MATMUTRPA_000000101.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>101</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235558_MATMUTRPA_000000084.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001428_MATMUTRPA_000000102.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-511d976d-b673-4616-b1d9-9e81134c4b9a.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144417_MATMUTRPA_000000102.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>102</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235558_MATMUTRPA_000000085.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001428_MATMUTRPA_000000103.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-5dd7dfad-d899-4d3b-a948-16f50763249c.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144418_MATMUTRPA_000000103.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>103</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235559_MATMUTRPA_000000086.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001429_MATMUTRPA_000000104.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-5dee5d56-af0d-46cb-bacc-b7045d169bf1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144419_MATMUTRPA_000000104.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>104</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235559_MATMUTRPA_000000087.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001429_MATMUTRPA_000000105.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-5effc335-5e66-4e89-b745-0ceb6dc2c5c5.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144419_MATMUTRPA_000000105.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>105</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\20250729_235559_MATMUTRPA_000000088.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001430_MATMUTRPA_000000106.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-639a98d2-4d8b-435f-8ce8-5a057d8b78c1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144420_MATMUTRPA_000000106.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>106</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\28284-12900402-NOTIF-2024-11-22-13100402-be8b2fde-eaa7-4fef-9c86-f9cf394a9158-f05448874c204e8f97c5021cace221e9.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001430_MATMUTRPA_000000107.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-6704a614-5d1d-45b6-baba-c9cec9602725.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144421_MATMUTRPA_000000107.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>107</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\40763-04550404-NOTIF-2024-11-22-13100402-17c8e4dd-5ea3-4b7d-b981-ce1fc8701fe5-626f4115dcfd47e5bb8684b4302becbc.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001431_MATMUTRPA_000000108.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-6e8fb98b-af36-48fc-8783-522c7503abf0.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144422_MATMUTRPA_000000108.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>108</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\40763-04550404-NOTIF-2024-11-22-13100402-398ccc85-4870-4ac2-a681-2341e8942eec-acdc01e31a644e0897669be1340a2bed.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001431_MATMUTRPA_000000109.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-862c1b42-9ca9-4924-90b0-2add3d55dac1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144422_MATMUTRPA_000000109.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>109</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\a.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001432_MATMUTRPA_000000110.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-87eb1dd7-d4f7-4fc7-844f-30c91916f02e.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144423_MATMUTRPA_000000110.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>110</x:t>
   </x:si>
   <x:si>
-    <x:t>20250808_001432_MATMUTRPA_000000111.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-8b93f0c7-0ce0-4043-9076-2f4ead2f6138.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144424_MATMUTRPA_000000111.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>111</x:t>
   </x:si>
   <x:si>
-    <x:t>20250808_001432_MATMUTRPA_000000112.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-9347e787-ae92-415a-a649-74f85e64cadc.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144424_MATMUTRPA_000000112.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>112</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T135427.629.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001433_MATMUTRPA_000000114.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-9c432c50-7279-4cd1-af92-6731fbf41cd7.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144425_MATMUTRPA_000000113.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>113</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-9c98cb9f-999e-4847-a360-b1b442ff7fb2.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144426_MATMUTRPA_000000114.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>114</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T135602.938.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001433_MATMUTRPA_000000115.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-9f675ec0-f692-481f-ab22-339db6b5c823.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144427_MATMUTRPA_000000115.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>115</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T135729.486.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001434_MATMUTRPA_000000116.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-ab2cdf1d-96cc-40f7-a5d1-2eed4bb8c1a8.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144427_MATMUTRPA_000000116.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>116</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T140113.150.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001434_MATMUTRPA_000000117.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-b14c24a0-df7f-4867-9af7-7684384f7cf4.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144428_MATMUTRPA_000000117.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>117</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T140229.156.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001435_MATMUTRPA_000000118.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-b1acac80-cd9a-404f-9b5c-1f12c4f0b3d1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144429_MATMUTRPA_000000118.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>118</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T140312.416.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001435_MATMUTRPA_000000119.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-b5f51aef-7f38-4d58-95c3-5d21eb9d3e8f.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144429_MATMUTRPA_000000119.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>119</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T140407.802.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001435_MATMUTRPA_000000120.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-b8b50afc-4c0b-4baa-ad53-0da3585df128.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144430_MATMUTRPA_000000120.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>120</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T140503.945.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001436_MATMUTRPA_000000121.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-c2f71dca-64b8-44d6-a5b6-88dc1e338034.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144431_MATMUTRPA_000000121.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>121</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T140554.081.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001436_MATMUTRPA_000000122.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-c544fba4-fd1a-478c-b5fe-ad7a98d83837.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144431_MATMUTRPA_000000122.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>122</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T140635.034.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001437_MATMUTRPA_000000123.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-c76eeee5-6d36-453a-8263-c16fd1da92c8.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144432_MATMUTRPA_000000123.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>123</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T140722.293.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001437_MATMUTRPA_000000124.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-caef8afe-5917-4618-b8c7-4e3da45467d3.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144433_MATMUTRPA_000000124.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>124</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T140820.205.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001437_MATMUTRPA_000000125.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-cf45e6ae-3326-4774-8b4c-649c088cc2d1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144433_MATMUTRPA_000000125.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>125</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T140909.695.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001438_MATMUTRPA_000000126.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-da489881-d2e3-4ef1-9711-2611be3b4090.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144434_MATMUTRPA_000000126.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>126</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T140949.978.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001438_MATMUTRPA_000000127.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-e4af891b-489e-41f8-91e3-231ab61cf5b1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144435_MATMUTRPA_000000127.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>127</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T141038.018.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001439_MATMUTRPA_000000128.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-ec450215-2d71-492b-a8fc-5cfbf3eefff8.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144436_MATMUTRPA_000000128.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>128</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T141117.536.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001439_MATMUTRPA_000000129.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-edbc96f1-f7f3-4d49-8289-c5d79161b984.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144436_MATMUTRPA_000000129.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>129</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T141207.446.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001439_MATMUTRPA_000000130.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-fde41c47-c3ec-433a-85d4-ba6300678a48.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144437_MATMUTRPA_000000130.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>130</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T141322.570.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001440_MATMUTRPA_000000131.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-fea503bc-7ab5-4676-9a12-0037e9b64197.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144438_MATMUTRPA_000000131.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>131</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T141417.553.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001440_MATMUTRPA_000000132.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-ff89c62b-722a-4e3c-a633-02d8ae58d348.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144438_MATMUTRPA_000000132.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>132</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\Demande de resiliation Hamon - 2024-11-25T141514.019.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001441_MATMUTRPA_000000133.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-ffe34624-db37-4b42-9319-c6fa38769538.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144439_MATMUTRPA_000000133.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>133</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\1732366193</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001441_MATMUTRPA_000000134.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-030f5bfd-1113-4138-9749-c114a871e88c.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144440_MATMUTRPA_000000134.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>134</x:t>
   </x:si>
   <x:si>
-    <x:t>Oui</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\2281907752</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001442_MATMUTRPA_000000135.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-0d8bcc33-75ee-4717-ab8c-9c317ac942aa.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144440_MATMUTRPA_000000135.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>135</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\2095807535</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001442_MATMUTRPA_000000136.pdf</x:t>
+    <x:t>BE014 - [200209005929Q | la clé extraite Q   est différente de la clé générée U] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-4269d6d1-341d-4cbc-a71e-d00aa13f0fdd.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144441_MATMUTRPA_000000136.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>136</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\3332348086</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001443_MATMUTRPA_000000137.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-4add1608-3e4b-4bde-9bf4-fb1635da3518.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144442_MATMUTRPA_000000137.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>137</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\2037793408</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001443_MATMUTRPA_000000138.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-4b81cdd8-ed5d-4642-9774-a0991aab605a.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144442_MATMUTRPA_000000138.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>138</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\7766679772</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001444_MATMUTRPA_000000139.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-4ffbf570-f356-4ad7-8dc2-3bbe887ea42f.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144443_MATMUTRPA_000000139.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>139</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\1009512117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001444_MATMUTRPA_000000140.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-6635e8e7-7bbe-47ec-8d0f-e3ae14e1d08a.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144444_MATMUTRPA_000000140.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>140</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\6544809077</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001445_MATMUTRPA_000000141.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-6f57bddf-4c41-46aa-b7cf-7a4a61152ff2.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144445_MATMUTRPA_000000141.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>141</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\6364486263</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001445_MATMUTRPA_000000142.pdf</x:t>
+    <x:t>BE014 - [941100007093n | la clé extraite n   est différente de la clé générée S] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-75efcddd-7b66-4b08-96b3-7f163f37a5d2.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144445_MATMUTRPA_000000142.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>142</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\9432160377</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001446_MATMUTRPA_000000143.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-818e18bb-5359-4e2e-a365-ca5dcc2ba43e.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144446_MATMUTRPA_000000143.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>143</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\1879992102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001446_MATMUTRPA_000000144.pdf</x:t>
+    <x:t>BE014 - [980000790056R | la clé extraite R   est différente de la clé générée V] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-951d5cc1-89f3-4898-aa04-b7ef3f640038.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144447_MATMUTRPA_000000144.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>144</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\5988929419</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001446_MATMUTRPA_000000145.pdf</x:t>
+    <x:t>BE014 - [980003071043N | la clé extraite N   est différente de la clé générée S] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-9562fdc3-ce0b-47e5-be2e-57d90ef0b482.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144447_MATMUTRPA_000000145.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>145</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\9016932803</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001447_MATMUTRPA_000000146.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-986b17de-a3f8-4439-9056-eb5a9b081769.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144448_MATMUTRPA_000000146.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>146</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\message_43310327_resiliation@matmut.fr.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001447_MATMUTRPA_000000147.pdf</x:t>
+    <x:t>BE014 - [980003236201D | la clé extraite D   est différente de la clé générée R] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-a223cb74-6dd5-41ac-9080-f8896cb4fd91.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144449_MATMUTRPA_000000147.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>147</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\message_43310334_resiliation@matmut.fr.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001448_MATMUTRPA_000000148.pdf</x:t>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-c253907c-e75f-48e1-95bb-f17e815b7d9e.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144450_MATMUTRPA_000000148.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>148</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\message_43310361_resiliation@matmut.fr.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001448_MATMUTRPA_000000149.pdf</x:t>
+    <x:t>BE014 - [980003776917Q | la clé extraite Q   est différente de la clé générée U] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-da19c964-68bd-46ae-b867-c00319278874.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144451_MATMUTRPA_000000149.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>149</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\message_43310674_resiliation@matmut.fr.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001449_MATMUTRPA_000000150.pdf</x:t>
+    <x:t>BE014 - [980003544355Y | la clé extraite Y   est différente de la clé générée C] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-dc219e73-57b8-476f-bf37-81013502ec86.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144451_MATMUTRPA_000000150.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>150</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\message_43335289_resiliation@matmut.fr.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001450_MATMUTRPA_000000151.pdf</x:t>
+    <x:t>BE014 - [980002460150Y | la clé extraite Y   est différente de la clé générée C] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-e767552f-bec9-4f74-a950-91b6e2d51a39.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144452_MATMUTRPA_000000151.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>151</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\message_43379712_resiliation@matmut.fr.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001450_MATMUTRPA_000000152.pdf</x:t>
+    <x:t>BE014 - [139100002235P | la clé extraite P   est différente de la clé générée T] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-f31075a6-6584-4298-b5c5-fb27b0d71eca.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250813_144453_MATMUTRPA_000000152.pdf</x:t>
   </x:si>
   <x:si>
     <x:t>152</x:t>
   </x:si>
   <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\message_43425700_resiliation@matmut.fr.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001451_MATMUTRPA_000000153.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_600-873846be-1a72-46f8-99b1-96a162f0e422.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001451_MATMUTRPA_000000154.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_600-a4d7dc50-1859-42d5-8719-089e9b9dde71.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001452_MATMUTRPA_000000155.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_600-a87518f5-6477-42a0-bebc-18c0f42df781.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001452_MATMUTRPA_000000156.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>156</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_600-ba00efcc-5cf9-4fef-84f4-2014e001ec49.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001453_MATMUTRPA_000000157.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_600-cbb3e6bc-cf3e-4aa1-bc80-7e48c234e478.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001453_MATMUTRPA_000000158.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>158</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_600-d81d8a6b-1e4c-4e63-b367-d9b8886c6d9a.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001454_MATMUTRPA_000000159.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>159</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_600-d8d535d2-0678-41f4-815f-04dff1d2dd0c.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001454_MATMUTRPA_000000160.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_600-dca5a1ab-31e9-47b8-8c86-d8e5f682607e.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001454_MATMUTRPA_000000161.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>161</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_600-e4947664-09fe-4856-91fa-a54ffced7ee6.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001455_MATMUTRPA_000000162.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_600-e55206cb-5ecf-4568-9183-a280a60e41c1.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001455_MATMUTRPA_000000163.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_600-eeb82fcb-dfb1-4b9a-9bff-e411581472ce.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001456_MATMUTRPA_000000164.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>164</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_600-f301cec9-984a-450e-b224-c563f5203433.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001456_MATMUTRPA_000000165.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-02e06e81-c885-431d-a456-60ab127dc071.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001457_MATMUTRPA_000000166.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>166</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-1715cf71-724d-45b6-8e15-e86c557419a4.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001457_MATMUTRPA_000000167.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>167</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-1876f30c-83a4-4a4c-9c55-094fdf3ac844.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001458_MATMUTRPA_000000168.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-1c7cbc6f-6bb2-4b7b-9968-ca6bc78fe996.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001458_MATMUTRPA_000000169.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-23557855-7620-4ae5-9241-fcc4412132a8.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001459_MATMUTRPA_000000170.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>170</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-23e9ee7b-1c83-4124-9a3b-1f8b9052a987.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001459_MATMUTRPA_000000171.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>171</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-338f2191-3f8d-4d87-9910-2483cf9753d1.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001500_MATMUTRPA_000000172.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-38ca5ea7-46a9-422d-a449-10947af6f55a.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001500_MATMUTRPA_000000173.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-3c267d7a-d52b-4492-a732-7a3e45159f79.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001501_MATMUTRPA_000000174.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-3df6b24f-3c10-49d2-bef4-85d02d4d32c8.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001501_MATMUTRPA_000000175.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-40f6d100-df71-4cb6-b435-c92ee1b7a806.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001502_MATMUTRPA_000000176.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-43115be2-cca2-44d8-bb9c-2abec01bff83.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001502_MATMUTRPA_000000177.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-4ac8d681-6792-426f-a1d9-97439fdd85b0.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001503_MATMUTRPA_000000178.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-4f14000d-93a1-4515-80d8-b2647251b2e4.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001503_MATMUTRPA_000000179.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-50842b6b-c5bf-4c18-bc16-877c4c658790.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001504_MATMUTRPA_000000180.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-511d976d-b673-4616-b1d9-9e81134c4b9a.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001504_MATMUTRPA_000000181.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-5dd7dfad-d899-4d3b-a948-16f50763249c.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001505_MATMUTRPA_000000182.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-5dee5d56-af0d-46cb-bacc-b7045d169bf1.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001505_MATMUTRPA_000000183.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-5effc335-5e66-4e89-b745-0ceb6dc2c5c5.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001506_MATMUTRPA_000000184.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-639a98d2-4d8b-435f-8ce8-5a057d8b78c1.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001506_MATMUTRPA_000000185.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-6704a614-5d1d-45b6-baba-c9cec9602725.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001507_MATMUTRPA_000000186.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>186</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-6e8fb98b-af36-48fc-8783-522c7503abf0.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001507_MATMUTRPA_000000187.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-862c1b42-9ca9-4924-90b0-2add3d55dac1.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001508_MATMUTRPA_000000188.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-8b93f0c7-0ce0-4043-9076-2f4ead2f6138.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001509_MATMUTRPA_000000189.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-9347e787-ae92-415a-a649-74f85e64cadc.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001509_MATMUTRPA_000000190.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-9c432c50-7279-4cd1-af92-6731fbf41cd7.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001510_MATMUTRPA_000000191.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-9c98cb9f-999e-4847-a360-b1b442ff7fb2.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001511_MATMUTRPA_000000192.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-9f675ec0-f692-481f-ab22-339db6b5c823.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001512_MATMUTRPA_000000193.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>193</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-ab2cdf1d-96cc-40f7-a5d1-2eed4bb8c1a8.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001512_MATMUTRPA_000000194.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>194</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-b14c24a0-df7f-4867-9af7-7684384f7cf4.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001513_MATMUTRPA_000000195.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>195</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-b1acac80-cd9a-404f-9b5c-1f12c4f0b3d1.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001513_MATMUTRPA_000000196.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>196</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-b5f51aef-7f38-4d58-95c3-5d21eb9d3e8f.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001514_MATMUTRPA_000000197.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>197</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-b8b50afc-4c0b-4baa-ad53-0da3585df128.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001514_MATMUTRPA_000000198.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>198</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-c2f71dca-64b8-44d6-a5b6-88dc1e338034.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001515_MATMUTRPA_000000199.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>199</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-c544fba4-fd1a-478c-b5fe-ad7a98d83837.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001516_MATMUTRPA_000000200.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-c76eeee5-6d36-453a-8263-c16fd1da92c8.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001516_MATMUTRPA_000000201.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-caef8afe-5917-4618-b8c7-4e3da45467d3.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001517_MATMUTRPA_000000202.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>202</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-cf45e6ae-3326-4774-8b4c-649c088cc2d1.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001517_MATMUTRPA_000000203.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>203</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-da489881-d2e3-4ef1-9711-2611be3b4090.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001518_MATMUTRPA_000000204.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-e4af891b-489e-41f8-91e3-231ab61cf5b1.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001518_MATMUTRPA_000000205.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>205</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-ec450215-2d71-492b-a8fc-5cfbf3eefff8.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001519_MATMUTRPA_000000206.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>206</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-edbc96f1-f7f3-4d49-8289-c5d79161b984.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001520_MATMUTRPA_000000207.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>207</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-fea503bc-7ab5-4676-9a12-0037e9b64197.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001520_MATMUTRPA_000000208.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>208</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-ff89c62b-722a-4e3c-a633-02d8ae58d348.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001521_MATMUTRPA_000000209.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_700-ffe34624-db37-4b42-9319-c6fa38769538.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001521_MATMUTRPA_000000210.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-030f5bfd-1113-4138-9749-c114a871e88c.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001522_MATMUTRPA_000000211.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-0d8bcc33-75ee-4717-ab8c-9c317ac942aa.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001522_MATMUTRPA_000000212.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-4b81cdd8-ed5d-4642-9774-a0991aab605a.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001523_MATMUTRPA_000000213.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-4ffbf570-f356-4ad7-8dc2-3bbe887ea42f.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001523_MATMUTRPA_000000214.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-6635e8e7-7bbe-47ec-8d0f-e3ae14e1d08a.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001523_MATMUTRPA_000000215.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-6f57bddf-4c41-46aa-b7cf-7a4a61152ff2.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001524_MATMUTRPA_000000216.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>216</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-818e18bb-5359-4e2e-a365-ca5dcc2ba43e.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001524_MATMUTRPA_000000217.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>217</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-951d5cc1-89f3-4898-aa04-b7ef3f640038.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001525_MATMUTRPA_000000218.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>218</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-9562fdc3-ce0b-47e5-be2e-57d90ef0b482.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001525_MATMUTRPA_000000219.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>219</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-986b17de-a3f8-4439-9056-eb5a9b081769.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001526_MATMUTRPA_000000220.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>220</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-a223cb74-6dd5-41ac-9080-f8896cb4fd91.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001526_MATMUTRPA_000000221.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-c253907c-e75f-48e1-95bb-f17e815b7d9e.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001527_MATMUTRPA_000000222.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>222</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-da19c964-68bd-46ae-b867-c00319278874.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001527_MATMUTRPA_000000223.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>223</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-dc219e73-57b8-476f-bf37-81013502ec86.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001528_MATMUTRPA_000000224.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>224</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-e767552f-bec9-4f74-a950-91b6e2d51a39.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001528_MATMUTRPA_000000225.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>225</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\Users\Walid ABRA\Documents\TEST\4\tessi_777-f31075a6-6584-4298-b5c5-fb27b0d71eca.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250808_001530_MATMUTRPA_000000227.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>227</x:t>
+    <x:t>BE014 - [170609001247S | la clé extraite S   est différente de la clé générée E] BE014 - Clé num soc KO</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2 xr">
+<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2">
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
@@ -2407,7 +2001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -2457,9 +2051,12 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
@@ -2480,67 +2077,79 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
         <x:v>12</x:v>
@@ -2548,19 +2157,22 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
         <x:v>12</x:v>
@@ -2568,19 +2180,22 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
         <x:v>12</x:v>
@@ -2588,19 +2203,22 @@
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>12</x:v>
@@ -2608,19 +2226,22 @@
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>11</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
         <x:v>12</x:v>
@@ -2628,19 +2249,22 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>11</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>12</x:v>
@@ -2648,19 +2272,22 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
         <x:v>12</x:v>
@@ -2668,19 +2295,22 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
         <x:v>12</x:v>
@@ -2688,19 +2318,22 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
         <x:v>12</x:v>
@@ -2708,19 +2341,22 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
         <x:v>12</x:v>
@@ -2728,19 +2364,22 @@
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
         <x:v>12</x:v>
@@ -2748,19 +2387,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
         <x:v>12</x:v>
@@ -2768,19 +2410,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>12</x:v>
@@ -2788,22 +2433,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
         <x:v>12</x:v>
@@ -2811,22 +2456,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
         <x:v>12</x:v>
@@ -2834,22 +2479,22 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
         <x:v>12</x:v>
@@ -2857,22 +2502,22 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
         <x:v>12</x:v>
@@ -2880,22 +2525,22 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
         <x:v>12</x:v>
@@ -2903,22 +2548,22 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
         <x:v>12</x:v>
@@ -2926,22 +2571,22 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
         <x:v>12</x:v>
@@ -2949,22 +2594,22 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
         <x:v>12</x:v>
@@ -2972,22 +2617,22 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
         <x:v>12</x:v>
@@ -2995,22 +2640,22 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C28" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F28" s="0" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
         <x:v>12</x:v>
@@ -3018,22 +2663,22 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="B29" s="0" t="s">
+      <x:c r="E29" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="C29" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F29" s="0" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
         <x:v>12</x:v>
@@ -3041,22 +2686,22 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B30" s="0" t="s">
+      <x:c r="C30" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
+      <x:c r="E30" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="E30" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F30" s="0" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
         <x:v>12</x:v>
@@ -3076,10 +2721,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
         <x:v>12</x:v>
@@ -3087,22 +2732,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
         <x:v>12</x:v>
@@ -3110,22 +2755,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
         <x:v>12</x:v>
@@ -3133,22 +2778,22 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
         <x:v>12</x:v>
@@ -3156,22 +2801,22 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
         <x:v>12</x:v>
@@ -3179,22 +2824,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
         <x:v>12</x:v>
@@ -3202,22 +2847,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
         <x:v>12</x:v>
@@ -3225,22 +2870,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
         <x:v>12</x:v>
@@ -3248,22 +2893,22 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
         <x:v>12</x:v>
@@ -3271,22 +2916,22 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
         <x:v>12</x:v>
@@ -3294,22 +2939,22 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
         <x:v>12</x:v>
@@ -3317,22 +2962,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
         <x:v>12</x:v>
@@ -3340,22 +2985,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
         <x:v>12</x:v>
@@ -3363,22 +3008,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
         <x:v>12</x:v>
@@ -3386,22 +3031,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
         <x:v>12</x:v>
@@ -3409,22 +3054,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
         <x:v>12</x:v>
@@ -3432,22 +3077,22 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
         <x:v>12</x:v>
@@ -3455,22 +3100,22 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
         <x:v>12</x:v>
@@ -3478,22 +3123,22 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
         <x:v>12</x:v>
@@ -3501,22 +3146,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
         <x:v>12</x:v>
@@ -3524,22 +3169,22 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
         <x:v>12</x:v>
@@ -3547,22 +3192,22 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
         <x:v>12</x:v>
@@ -3570,22 +3215,22 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
         <x:v>12</x:v>
@@ -3593,22 +3238,22 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
         <x:v>12</x:v>
@@ -3616,22 +3261,22 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
         <x:v>12</x:v>
@@ -3639,22 +3284,22 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G56" s="0" t="s">
         <x:v>12</x:v>
@@ -3662,22 +3307,22 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G57" s="0" t="s">
         <x:v>12</x:v>
@@ -3685,22 +3330,22 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="G58" s="0" t="s">
         <x:v>12</x:v>
@@ -3708,22 +3353,22 @@
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G59" s="0" t="s">
         <x:v>12</x:v>
@@ -3731,22 +3376,22 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="G60" s="0" t="s">
         <x:v>12</x:v>
@@ -3754,298 +3399,298 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="G61" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G62" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="G63" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="G64" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="G65" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G66" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="G67" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G68" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="G69" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G70" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="G71" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="G72" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="G73" s="0" t="s">
         <x:v>12</x:v>
@@ -4053,22 +3698,22 @@
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="G74" s="0" t="s">
         <x:v>12</x:v>
@@ -4076,22 +3721,22 @@
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="G75" s="0" t="s">
         <x:v>12</x:v>
@@ -4099,22 +3744,22 @@
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G76" s="0" t="s">
         <x:v>12</x:v>
@@ -4122,22 +3767,22 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="G77" s="0" t="s">
         <x:v>12</x:v>
@@ -4145,22 +3790,22 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="G78" s="0" t="s">
         <x:v>12</x:v>
@@ -4168,22 +3813,22 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="G79" s="0" t="s">
         <x:v>12</x:v>
@@ -4191,22 +3836,22 @@
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="G80" s="0" t="s">
         <x:v>12</x:v>
@@ -4214,22 +3859,22 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="G81" s="0" t="s">
         <x:v>12</x:v>
@@ -4237,22 +3882,22 @@
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="G82" s="0" t="s">
         <x:v>12</x:v>
@@ -4260,22 +3905,22 @@
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="G83" s="0" t="s">
         <x:v>12</x:v>
@@ -4283,22 +3928,22 @@
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="G84" s="0" t="s">
         <x:v>12</x:v>
@@ -4306,22 +3951,22 @@
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="G85" s="0" t="s">
         <x:v>12</x:v>
@@ -4329,22 +3974,22 @@
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="G86" s="0" t="s">
         <x:v>12</x:v>
@@ -4352,22 +3997,22 @@
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="G87" s="0" t="s">
         <x:v>12</x:v>
@@ -4375,22 +4020,22 @@
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="G88" s="0" t="s">
         <x:v>12</x:v>
@@ -4398,22 +4043,22 @@
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="G89" s="0" t="s">
         <x:v>12</x:v>
@@ -4421,22 +4066,22 @@
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="G90" s="0" t="s">
         <x:v>12</x:v>
@@ -4444,22 +4089,22 @@
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="G91" s="0" t="s">
         <x:v>12</x:v>
@@ -4467,22 +4112,22 @@
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G92" s="0" t="s">
         <x:v>12</x:v>
@@ -4490,22 +4135,22 @@
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G93" s="0" t="s">
         <x:v>12</x:v>
@@ -4513,22 +4158,22 @@
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G94" s="0" t="s">
         <x:v>12</x:v>
@@ -4536,22 +4181,22 @@
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G95" s="0" t="s">
         <x:v>12</x:v>
@@ -4559,22 +4204,22 @@
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G96" s="0" t="s">
         <x:v>12</x:v>
@@ -4582,22 +4227,22 @@
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G97" s="0" t="s">
         <x:v>12</x:v>
@@ -4605,22 +4250,22 @@
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G98" s="0" t="s">
         <x:v>12</x:v>
@@ -4628,22 +4273,22 @@
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="G99" s="0" t="s">
         <x:v>12</x:v>
@@ -4651,22 +4296,22 @@
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G100" s="0" t="s">
         <x:v>12</x:v>
@@ -4674,22 +4319,22 @@
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G101" s="0" t="s">
         <x:v>12</x:v>
@@ -4697,22 +4342,22 @@
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G102" s="0" t="s">
         <x:v>12</x:v>
@@ -4720,22 +4365,22 @@
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G103" s="0" t="s">
         <x:v>12</x:v>
@@ -4743,22 +4388,22 @@
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G104" s="0" t="s">
         <x:v>12</x:v>
@@ -4766,22 +4411,22 @@
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G105" s="0" t="s">
         <x:v>12</x:v>
@@ -4789,22 +4434,22 @@
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G106" s="0" t="s">
         <x:v>12</x:v>
@@ -4812,19 +4457,22 @@
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F107" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G107" s="0" t="s">
         <x:v>12</x:v>
@@ -4832,19 +4480,22 @@
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F108" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G108" s="0" t="s">
         <x:v>12</x:v>
@@ -4852,19 +4503,22 @@
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F109" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G109" s="0" t="s">
         <x:v>12</x:v>
@@ -4872,19 +4526,22 @@
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F110" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G110" s="0" t="s">
         <x:v>12</x:v>
@@ -4892,19 +4549,22 @@
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F111" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G111" s="0" t="s">
         <x:v>12</x:v>
@@ -4912,19 +4572,22 @@
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F112" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G112" s="0" t="s">
         <x:v>12</x:v>
@@ -4932,19 +4595,22 @@
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F113" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G113" s="0" t="s">
         <x:v>12</x:v>
@@ -4952,19 +4618,22 @@
     </x:row>
     <x:row r="114" spans="1:7">
       <x:c r="A114" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F114" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G114" s="0" t="s">
         <x:v>12</x:v>
@@ -4972,19 +4641,22 @@
     </x:row>
     <x:row r="115" spans="1:7">
       <x:c r="A115" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F115" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G115" s="0" t="s">
         <x:v>12</x:v>
@@ -4992,19 +4664,22 @@
     </x:row>
     <x:row r="116" spans="1:7">
       <x:c r="A116" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F116" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G116" s="0" t="s">
         <x:v>12</x:v>
@@ -5012,19 +4687,22 @@
     </x:row>
     <x:row r="117" spans="1:7">
       <x:c r="A117" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F117" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G117" s="0" t="s">
         <x:v>12</x:v>
@@ -5032,19 +4710,22 @@
     </x:row>
     <x:row r="118" spans="1:7">
       <x:c r="A118" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F118" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G118" s="0" t="s">
         <x:v>12</x:v>
@@ -5052,19 +4733,22 @@
     </x:row>
     <x:row r="119" spans="1:7">
       <x:c r="A119" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F119" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G119" s="0" t="s">
         <x:v>12</x:v>
@@ -5072,19 +4756,22 @@
     </x:row>
     <x:row r="120" spans="1:7">
       <x:c r="A120" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F120" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G120" s="0" t="s">
         <x:v>12</x:v>
@@ -5092,19 +4779,22 @@
     </x:row>
     <x:row r="121" spans="1:7">
       <x:c r="A121" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F121" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G121" s="0" t="s">
         <x:v>12</x:v>
@@ -5112,19 +4802,22 @@
     </x:row>
     <x:row r="122" spans="1:7">
       <x:c r="A122" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F122" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G122" s="0" t="s">
         <x:v>12</x:v>
@@ -5132,19 +4825,22 @@
     </x:row>
     <x:row r="123" spans="1:7">
       <x:c r="A123" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F123" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G123" s="0" t="s">
         <x:v>12</x:v>
@@ -5152,19 +4848,22 @@
     </x:row>
     <x:row r="124" spans="1:7">
       <x:c r="A124" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F124" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G124" s="0" t="s">
         <x:v>12</x:v>
@@ -5172,19 +4871,22 @@
     </x:row>
     <x:row r="125" spans="1:7">
       <x:c r="A125" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F125" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G125" s="0" t="s">
         <x:v>12</x:v>
@@ -5192,19 +4894,22 @@
     </x:row>
     <x:row r="126" spans="1:7">
       <x:c r="A126" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F126" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G126" s="0" t="s">
         <x:v>12</x:v>
@@ -5212,19 +4917,22 @@
     </x:row>
     <x:row r="127" spans="1:7">
       <x:c r="A127" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F127" s="0" t="s">
+        <x:v>356</x:v>
       </x:c>
       <x:c r="G127" s="0" t="s">
         <x:v>12</x:v>
@@ -5232,19 +4940,22 @@
     </x:row>
     <x:row r="128" spans="1:7">
       <x:c r="A128" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F128" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G128" s="0" t="s">
         <x:v>12</x:v>
@@ -5252,19 +4963,22 @@
     </x:row>
     <x:row r="129" spans="1:7">
       <x:c r="A129" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F129" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G129" s="0" t="s">
         <x:v>12</x:v>
@@ -5272,19 +4986,22 @@
     </x:row>
     <x:row r="130" spans="1:7">
       <x:c r="A130" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F130" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G130" s="0" t="s">
         <x:v>12</x:v>
@@ -5292,19 +5009,22 @@
     </x:row>
     <x:row r="131" spans="1:7">
       <x:c r="A131" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F131" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G131" s="0" t="s">
         <x:v>12</x:v>
@@ -5312,19 +5032,22 @@
     </x:row>
     <x:row r="132" spans="1:7">
       <x:c r="A132" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F132" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G132" s="0" t="s">
         <x:v>12</x:v>
@@ -5332,279 +5055,321 @@
     </x:row>
     <x:row r="133" spans="1:7">
       <x:c r="A133" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F133" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G133" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:7">
       <x:c r="A134" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F134" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G134" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:7">
       <x:c r="A135" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F135" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G135" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:7">
       <x:c r="A136" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F136" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G136" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:7">
       <x:c r="A137" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F137" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G137" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:7">
       <x:c r="A138" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F138" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G138" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:7">
       <x:c r="A139" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F139" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G139" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:7">
       <x:c r="A140" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F140" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G140" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:7">
       <x:c r="A141" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F141" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G141" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:7">
       <x:c r="A142" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F142" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G142" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:7">
       <x:c r="A143" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F143" s="0" t="s">
+        <x:v>489</x:v>
       </x:c>
       <x:c r="G143" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:7">
       <x:c r="A144" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F144" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G144" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:7">
       <x:c r="A145" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F145" s="0" t="s">
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G145" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:7">
       <x:c r="A146" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F146" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G146" s="0" t="s">
         <x:v>12</x:v>
@@ -5612,19 +5377,22 @@
     </x:row>
     <x:row r="147" spans="1:7">
       <x:c r="A147" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F147" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G147" s="0" t="s">
         <x:v>12</x:v>
@@ -5632,19 +5400,22 @@
     </x:row>
     <x:row r="148" spans="1:7">
       <x:c r="A148" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F148" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G148" s="0" t="s">
         <x:v>12</x:v>
@@ -5652,19 +5423,22 @@
     </x:row>
     <x:row r="149" spans="1:7">
       <x:c r="A149" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F149" s="0" t="s">
+        <x:v>508</x:v>
       </x:c>
       <x:c r="G149" s="0" t="s">
         <x:v>12</x:v>
@@ -5672,19 +5446,22 @@
     </x:row>
     <x:row r="150" spans="1:7">
       <x:c r="A150" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F150" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G150" s="0" t="s">
         <x:v>12</x:v>
@@ -5692,19 +5469,22 @@
     </x:row>
     <x:row r="151" spans="1:7">
       <x:c r="A151" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F151" s="0" t="s">
+        <x:v>515</x:v>
       </x:c>
       <x:c r="G151" s="0" t="s">
         <x:v>12</x:v>
@@ -5712,19 +5492,22 @@
     </x:row>
     <x:row r="152" spans="1:7">
       <x:c r="A152" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F152" s="0" t="s">
+        <x:v>519</x:v>
       </x:c>
       <x:c r="G152" s="0" t="s">
         <x:v>12</x:v>
@@ -5732,19 +5515,22 @@
     </x:row>
     <x:row r="153" spans="1:7">
       <x:c r="A153" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F153" s="0" t="s">
+        <x:v>508</x:v>
       </x:c>
       <x:c r="G153" s="0" t="s">
         <x:v>12</x:v>
@@ -5752,19 +5538,22 @@
     </x:row>
     <x:row r="154" spans="1:7">
       <x:c r="A154" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F154" s="0" t="s">
+        <x:v>526</x:v>
       </x:c>
       <x:c r="G154" s="0" t="s">
         <x:v>12</x:v>
@@ -5772,19 +5561,22 @@
     </x:row>
     <x:row r="155" spans="1:7">
       <x:c r="A155" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F155" s="0" t="s">
+        <x:v>489</x:v>
       </x:c>
       <x:c r="G155" s="0" t="s">
         <x:v>12</x:v>
@@ -5792,19 +5584,22 @@
     </x:row>
     <x:row r="156" spans="1:7">
       <x:c r="A156" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F156" s="0" t="s">
+        <x:v>533</x:v>
       </x:c>
       <x:c r="G156" s="0" t="s">
         <x:v>12</x:v>
@@ -5812,19 +5607,22 @@
     </x:row>
     <x:row r="157" spans="1:7">
       <x:c r="A157" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F157" s="0" t="s">
+        <x:v>537</x:v>
       </x:c>
       <x:c r="G157" s="0" t="s">
         <x:v>12</x:v>
@@ -5832,19 +5630,22 @@
     </x:row>
     <x:row r="158" spans="1:7">
       <x:c r="A158" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F158" s="0" t="s">
+        <x:v>541</x:v>
       </x:c>
       <x:c r="G158" s="0" t="s">
         <x:v>12</x:v>
@@ -5852,19 +5653,22 @@
     </x:row>
     <x:row r="159" spans="1:7">
       <x:c r="A159" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F159" s="0" t="s">
+        <x:v>545</x:v>
       </x:c>
       <x:c r="G159" s="0" t="s">
         <x:v>12</x:v>
@@ -5872,1324 +5676,24 @@
     </x:row>
     <x:row r="160" spans="1:7">
       <x:c r="A160" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F160" s="0" t="s">
+        <x:v>549</x:v>
       </x:c>
       <x:c r="G160" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" spans="1:7">
-      <x:c r="A161" s="0" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="B161" s="0" t="s">
-        <x:v>491</x:v>
-      </x:c>
-      <x:c r="C161" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D161" s="0" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="E161" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G161" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162" spans="1:7">
-      <x:c r="A162" s="0" t="s">
-        <x:v>493</x:v>
-      </x:c>
-      <x:c r="B162" s="0" t="s">
-        <x:v>494</x:v>
-      </x:c>
-      <x:c r="C162" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D162" s="0" t="s">
-        <x:v>495</x:v>
-      </x:c>
-      <x:c r="E162" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G162" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163" spans="1:7">
-      <x:c r="A163" s="0" t="s">
-        <x:v>496</x:v>
-      </x:c>
-      <x:c r="B163" s="0" t="s">
-        <x:v>497</x:v>
-      </x:c>
-      <x:c r="C163" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D163" s="0" t="s">
-        <x:v>498</x:v>
-      </x:c>
-      <x:c r="E163" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G163" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164" spans="1:7">
-      <x:c r="A164" s="0" t="s">
-        <x:v>499</x:v>
-      </x:c>
-      <x:c r="B164" s="0" t="s">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="C164" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D164" s="0" t="s">
-        <x:v>501</x:v>
-      </x:c>
-      <x:c r="E164" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G164" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165" spans="1:7">
-      <x:c r="A165" s="0" t="s">
-        <x:v>502</x:v>
-      </x:c>
-      <x:c r="B165" s="0" t="s">
-        <x:v>503</x:v>
-      </x:c>
-      <x:c r="C165" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D165" s="0" t="s">
-        <x:v>504</x:v>
-      </x:c>
-      <x:c r="E165" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G165" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166" spans="1:7">
-      <x:c r="A166" s="0" t="s">
-        <x:v>505</x:v>
-      </x:c>
-      <x:c r="B166" s="0" t="s">
-        <x:v>506</x:v>
-      </x:c>
-      <x:c r="C166" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D166" s="0" t="s">
-        <x:v>507</x:v>
-      </x:c>
-      <x:c r="E166" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G166" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167" spans="1:7">
-      <x:c r="A167" s="0" t="s">
-        <x:v>508</x:v>
-      </x:c>
-      <x:c r="B167" s="0" t="s">
-        <x:v>509</x:v>
-      </x:c>
-      <x:c r="C167" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D167" s="0" t="s">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="E167" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G167" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168" spans="1:7">
-      <x:c r="A168" s="0" t="s">
-        <x:v>511</x:v>
-      </x:c>
-      <x:c r="B168" s="0" t="s">
-        <x:v>512</x:v>
-      </x:c>
-      <x:c r="C168" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D168" s="0" t="s">
-        <x:v>513</x:v>
-      </x:c>
-      <x:c r="E168" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G168" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" spans="1:7">
-      <x:c r="A169" s="0" t="s">
-        <x:v>514</x:v>
-      </x:c>
-      <x:c r="B169" s="0" t="s">
-        <x:v>515</x:v>
-      </x:c>
-      <x:c r="C169" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D169" s="0" t="s">
-        <x:v>516</x:v>
-      </x:c>
-      <x:c r="E169" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G169" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" spans="1:7">
-      <x:c r="A170" s="0" t="s">
-        <x:v>517</x:v>
-      </x:c>
-      <x:c r="B170" s="0" t="s">
-        <x:v>518</x:v>
-      </x:c>
-      <x:c r="C170" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D170" s="0" t="s">
-        <x:v>519</x:v>
-      </x:c>
-      <x:c r="E170" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G170" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" spans="1:7">
-      <x:c r="A171" s="0" t="s">
-        <x:v>520</x:v>
-      </x:c>
-      <x:c r="B171" s="0" t="s">
-        <x:v>521</x:v>
-      </x:c>
-      <x:c r="C171" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D171" s="0" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="E171" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G171" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" spans="1:7">
-      <x:c r="A172" s="0" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="B172" s="0" t="s">
-        <x:v>524</x:v>
-      </x:c>
-      <x:c r="C172" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D172" s="0" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="E172" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G172" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" spans="1:7">
-      <x:c r="A173" s="0" t="s">
-        <x:v>526</x:v>
-      </x:c>
-      <x:c r="B173" s="0" t="s">
-        <x:v>527</x:v>
-      </x:c>
-      <x:c r="C173" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D173" s="0" t="s">
-        <x:v>528</x:v>
-      </x:c>
-      <x:c r="E173" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G173" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174" spans="1:7">
-      <x:c r="A174" s="0" t="s">
-        <x:v>529</x:v>
-      </x:c>
-      <x:c r="B174" s="0" t="s">
-        <x:v>530</x:v>
-      </x:c>
-      <x:c r="C174" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D174" s="0" t="s">
-        <x:v>531</x:v>
-      </x:c>
-      <x:c r="E174" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G174" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" spans="1:7">
-      <x:c r="A175" s="0" t="s">
-        <x:v>532</x:v>
-      </x:c>
-      <x:c r="B175" s="0" t="s">
-        <x:v>533</x:v>
-      </x:c>
-      <x:c r="C175" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D175" s="0" t="s">
-        <x:v>534</x:v>
-      </x:c>
-      <x:c r="E175" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G175" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176" spans="1:7">
-      <x:c r="A176" s="0" t="s">
-        <x:v>535</x:v>
-      </x:c>
-      <x:c r="B176" s="0" t="s">
-        <x:v>536</x:v>
-      </x:c>
-      <x:c r="C176" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D176" s="0" t="s">
-        <x:v>537</x:v>
-      </x:c>
-      <x:c r="E176" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G176" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="177" spans="1:7">
-      <x:c r="A177" s="0" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="B177" s="0" t="s">
-        <x:v>539</x:v>
-      </x:c>
-      <x:c r="C177" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D177" s="0" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="E177" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G177" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="178" spans="1:7">
-      <x:c r="A178" s="0" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="B178" s="0" t="s">
-        <x:v>542</x:v>
-      </x:c>
-      <x:c r="C178" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D178" s="0" t="s">
-        <x:v>543</x:v>
-      </x:c>
-      <x:c r="E178" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G178" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179" spans="1:7">
-      <x:c r="A179" s="0" t="s">
-        <x:v>544</x:v>
-      </x:c>
-      <x:c r="B179" s="0" t="s">
-        <x:v>545</x:v>
-      </x:c>
-      <x:c r="C179" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D179" s="0" t="s">
-        <x:v>546</x:v>
-      </x:c>
-      <x:c r="E179" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G179" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="180" spans="1:7">
-      <x:c r="A180" s="0" t="s">
-        <x:v>547</x:v>
-      </x:c>
-      <x:c r="B180" s="0" t="s">
-        <x:v>548</x:v>
-      </x:c>
-      <x:c r="C180" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D180" s="0" t="s">
-        <x:v>549</x:v>
-      </x:c>
-      <x:c r="E180" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G180" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="181" spans="1:7">
-      <x:c r="A181" s="0" t="s">
-        <x:v>550</x:v>
-      </x:c>
-      <x:c r="B181" s="0" t="s">
-        <x:v>551</x:v>
-      </x:c>
-      <x:c r="C181" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D181" s="0" t="s">
-        <x:v>552</x:v>
-      </x:c>
-      <x:c r="E181" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G181" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="182" spans="1:7">
-      <x:c r="A182" s="0" t="s">
-        <x:v>553</x:v>
-      </x:c>
-      <x:c r="B182" s="0" t="s">
-        <x:v>554</x:v>
-      </x:c>
-      <x:c r="C182" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D182" s="0" t="s">
-        <x:v>555</x:v>
-      </x:c>
-      <x:c r="E182" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G182" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="183" spans="1:7">
-      <x:c r="A183" s="0" t="s">
-        <x:v>556</x:v>
-      </x:c>
-      <x:c r="B183" s="0" t="s">
-        <x:v>557</x:v>
-      </x:c>
-      <x:c r="C183" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D183" s="0" t="s">
-        <x:v>558</x:v>
-      </x:c>
-      <x:c r="E183" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G183" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="184" spans="1:7">
-      <x:c r="A184" s="0" t="s">
-        <x:v>559</x:v>
-      </x:c>
-      <x:c r="B184" s="0" t="s">
-        <x:v>560</x:v>
-      </x:c>
-      <x:c r="C184" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D184" s="0" t="s">
-        <x:v>561</x:v>
-      </x:c>
-      <x:c r="E184" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G184" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="185" spans="1:7">
-      <x:c r="A185" s="0" t="s">
-        <x:v>562</x:v>
-      </x:c>
-      <x:c r="B185" s="0" t="s">
-        <x:v>563</x:v>
-      </x:c>
-      <x:c r="C185" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D185" s="0" t="s">
-        <x:v>564</x:v>
-      </x:c>
-      <x:c r="E185" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G185" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="186" spans="1:7">
-      <x:c r="A186" s="0" t="s">
-        <x:v>565</x:v>
-      </x:c>
-      <x:c r="B186" s="0" t="s">
-        <x:v>566</x:v>
-      </x:c>
-      <x:c r="C186" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D186" s="0" t="s">
-        <x:v>567</x:v>
-      </x:c>
-      <x:c r="E186" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G186" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="187" spans="1:7">
-      <x:c r="A187" s="0" t="s">
-        <x:v>568</x:v>
-      </x:c>
-      <x:c r="B187" s="0" t="s">
-        <x:v>569</x:v>
-      </x:c>
-      <x:c r="C187" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D187" s="0" t="s">
-        <x:v>570</x:v>
-      </x:c>
-      <x:c r="E187" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G187" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="188" spans="1:7">
-      <x:c r="A188" s="0" t="s">
-        <x:v>571</x:v>
-      </x:c>
-      <x:c r="B188" s="0" t="s">
-        <x:v>572</x:v>
-      </x:c>
-      <x:c r="C188" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D188" s="0" t="s">
-        <x:v>573</x:v>
-      </x:c>
-      <x:c r="E188" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G188" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="189" spans="1:7">
-      <x:c r="A189" s="0" t="s">
-        <x:v>574</x:v>
-      </x:c>
-      <x:c r="B189" s="0" t="s">
-        <x:v>575</x:v>
-      </x:c>
-      <x:c r="C189" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D189" s="0" t="s">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="E189" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G189" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="190" spans="1:7">
-      <x:c r="A190" s="0" t="s">
-        <x:v>577</x:v>
-      </x:c>
-      <x:c r="B190" s="0" t="s">
-        <x:v>578</x:v>
-      </x:c>
-      <x:c r="C190" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D190" s="0" t="s">
-        <x:v>579</x:v>
-      </x:c>
-      <x:c r="E190" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G190" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="191" spans="1:7">
-      <x:c r="A191" s="0" t="s">
-        <x:v>580</x:v>
-      </x:c>
-      <x:c r="B191" s="0" t="s">
-        <x:v>581</x:v>
-      </x:c>
-      <x:c r="C191" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D191" s="0" t="s">
-        <x:v>582</x:v>
-      </x:c>
-      <x:c r="E191" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G191" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="192" spans="1:7">
-      <x:c r="A192" s="0" t="s">
-        <x:v>583</x:v>
-      </x:c>
-      <x:c r="B192" s="0" t="s">
-        <x:v>584</x:v>
-      </x:c>
-      <x:c r="C192" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D192" s="0" t="s">
-        <x:v>585</x:v>
-      </x:c>
-      <x:c r="E192" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G192" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="193" spans="1:7">
-      <x:c r="A193" s="0" t="s">
-        <x:v>586</x:v>
-      </x:c>
-      <x:c r="B193" s="0" t="s">
-        <x:v>587</x:v>
-      </x:c>
-      <x:c r="C193" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D193" s="0" t="s">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c r="E193" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G193" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="194" spans="1:7">
-      <x:c r="A194" s="0" t="s">
-        <x:v>589</x:v>
-      </x:c>
-      <x:c r="B194" s="0" t="s">
-        <x:v>590</x:v>
-      </x:c>
-      <x:c r="C194" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D194" s="0" t="s">
-        <x:v>591</x:v>
-      </x:c>
-      <x:c r="E194" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G194" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="195" spans="1:7">
-      <x:c r="A195" s="0" t="s">
-        <x:v>592</x:v>
-      </x:c>
-      <x:c r="B195" s="0" t="s">
-        <x:v>593</x:v>
-      </x:c>
-      <x:c r="C195" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D195" s="0" t="s">
-        <x:v>594</x:v>
-      </x:c>
-      <x:c r="E195" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G195" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="196" spans="1:7">
-      <x:c r="A196" s="0" t="s">
-        <x:v>595</x:v>
-      </x:c>
-      <x:c r="B196" s="0" t="s">
-        <x:v>596</x:v>
-      </x:c>
-      <x:c r="C196" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D196" s="0" t="s">
-        <x:v>597</x:v>
-      </x:c>
-      <x:c r="E196" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G196" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="197" spans="1:7">
-      <x:c r="A197" s="0" t="s">
-        <x:v>598</x:v>
-      </x:c>
-      <x:c r="B197" s="0" t="s">
-        <x:v>599</x:v>
-      </x:c>
-      <x:c r="C197" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D197" s="0" t="s">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="E197" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G197" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="198" spans="1:7">
-      <x:c r="A198" s="0" t="s">
-        <x:v>601</x:v>
-      </x:c>
-      <x:c r="B198" s="0" t="s">
-        <x:v>602</x:v>
-      </x:c>
-      <x:c r="C198" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D198" s="0" t="s">
-        <x:v>603</x:v>
-      </x:c>
-      <x:c r="E198" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G198" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="199" spans="1:7">
-      <x:c r="A199" s="0" t="s">
-        <x:v>604</x:v>
-      </x:c>
-      <x:c r="B199" s="0" t="s">
-        <x:v>605</x:v>
-      </x:c>
-      <x:c r="C199" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D199" s="0" t="s">
-        <x:v>606</x:v>
-      </x:c>
-      <x:c r="E199" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G199" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="200" spans="1:7">
-      <x:c r="A200" s="0" t="s">
-        <x:v>607</x:v>
-      </x:c>
-      <x:c r="B200" s="0" t="s">
-        <x:v>608</x:v>
-      </x:c>
-      <x:c r="C200" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D200" s="0" t="s">
-        <x:v>609</x:v>
-      </x:c>
-      <x:c r="E200" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G200" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="201" spans="1:7">
-      <x:c r="A201" s="0" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="B201" s="0" t="s">
-        <x:v>611</x:v>
-      </x:c>
-      <x:c r="C201" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D201" s="0" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="E201" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G201" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="202" spans="1:7">
-      <x:c r="A202" s="0" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="B202" s="0" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="C202" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D202" s="0" t="s">
-        <x:v>615</x:v>
-      </x:c>
-      <x:c r="E202" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G202" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="203" spans="1:7">
-      <x:c r="A203" s="0" t="s">
-        <x:v>616</x:v>
-      </x:c>
-      <x:c r="B203" s="0" t="s">
-        <x:v>617</x:v>
-      </x:c>
-      <x:c r="C203" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D203" s="0" t="s">
-        <x:v>618</x:v>
-      </x:c>
-      <x:c r="E203" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G203" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204" spans="1:7">
-      <x:c r="A204" s="0" t="s">
-        <x:v>619</x:v>
-      </x:c>
-      <x:c r="B204" s="0" t="s">
-        <x:v>620</x:v>
-      </x:c>
-      <x:c r="C204" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D204" s="0" t="s">
-        <x:v>621</x:v>
-      </x:c>
-      <x:c r="E204" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G204" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="205" spans="1:7">
-      <x:c r="A205" s="0" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="B205" s="0" t="s">
-        <x:v>623</x:v>
-      </x:c>
-      <x:c r="C205" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D205" s="0" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="E205" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G205" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="206" spans="1:7">
-      <x:c r="A206" s="0" t="s">
-        <x:v>625</x:v>
-      </x:c>
-      <x:c r="B206" s="0" t="s">
-        <x:v>626</x:v>
-      </x:c>
-      <x:c r="C206" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D206" s="0" t="s">
-        <x:v>627</x:v>
-      </x:c>
-      <x:c r="E206" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G206" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="207" spans="1:7">
-      <x:c r="A207" s="0" t="s">
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="B207" s="0" t="s">
-        <x:v>629</x:v>
-      </x:c>
-      <x:c r="C207" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D207" s="0" t="s">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="E207" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G207" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="208" spans="1:7">
-      <x:c r="A208" s="0" t="s">
-        <x:v>631</x:v>
-      </x:c>
-      <x:c r="B208" s="0" t="s">
-        <x:v>632</x:v>
-      </x:c>
-      <x:c r="C208" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D208" s="0" t="s">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="E208" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G208" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="209" spans="1:7">
-      <x:c r="A209" s="0" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="B209" s="0" t="s">
-        <x:v>635</x:v>
-      </x:c>
-      <x:c r="C209" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D209" s="0" t="s">
-        <x:v>636</x:v>
-      </x:c>
-      <x:c r="E209" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G209" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="210" spans="1:7">
-      <x:c r="A210" s="0" t="s">
-        <x:v>637</x:v>
-      </x:c>
-      <x:c r="B210" s="0" t="s">
-        <x:v>638</x:v>
-      </x:c>
-      <x:c r="C210" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D210" s="0" t="s">
-        <x:v>639</x:v>
-      </x:c>
-      <x:c r="E210" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G210" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="211" spans="1:7">
-      <x:c r="A211" s="0" t="s">
-        <x:v>640</x:v>
-      </x:c>
-      <x:c r="B211" s="0" t="s">
-        <x:v>641</x:v>
-      </x:c>
-      <x:c r="C211" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D211" s="0" t="s">
-        <x:v>642</x:v>
-      </x:c>
-      <x:c r="E211" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G211" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="212" spans="1:7">
-      <x:c r="A212" s="0" t="s">
-        <x:v>643</x:v>
-      </x:c>
-      <x:c r="B212" s="0" t="s">
-        <x:v>644</x:v>
-      </x:c>
-      <x:c r="C212" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D212" s="0" t="s">
-        <x:v>645</x:v>
-      </x:c>
-      <x:c r="E212" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F212" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G212" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="213" spans="1:7">
-      <x:c r="A213" s="0" t="s">
-        <x:v>646</x:v>
-      </x:c>
-      <x:c r="B213" s="0" t="s">
-        <x:v>647</x:v>
-      </x:c>
-      <x:c r="C213" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D213" s="0" t="s">
-        <x:v>648</x:v>
-      </x:c>
-      <x:c r="E213" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G213" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="214" spans="1:7">
-      <x:c r="A214" s="0" t="s">
-        <x:v>649</x:v>
-      </x:c>
-      <x:c r="B214" s="0" t="s">
-        <x:v>650</x:v>
-      </x:c>
-      <x:c r="C214" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D214" s="0" t="s">
-        <x:v>651</x:v>
-      </x:c>
-      <x:c r="E214" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G214" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="215" spans="1:7">
-      <x:c r="A215" s="0" t="s">
-        <x:v>652</x:v>
-      </x:c>
-      <x:c r="B215" s="0" t="s">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="C215" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D215" s="0" t="s">
-        <x:v>654</x:v>
-      </x:c>
-      <x:c r="E215" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G215" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="216" spans="1:7">
-      <x:c r="A216" s="0" t="s">
-        <x:v>655</x:v>
-      </x:c>
-      <x:c r="B216" s="0" t="s">
-        <x:v>656</x:v>
-      </x:c>
-      <x:c r="C216" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D216" s="0" t="s">
-        <x:v>657</x:v>
-      </x:c>
-      <x:c r="E216" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G216" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="217" spans="1:7">
-      <x:c r="A217" s="0" t="s">
-        <x:v>658</x:v>
-      </x:c>
-      <x:c r="B217" s="0" t="s">
-        <x:v>659</x:v>
-      </x:c>
-      <x:c r="C217" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D217" s="0" t="s">
-        <x:v>660</x:v>
-      </x:c>
-      <x:c r="E217" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G217" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="218" spans="1:7">
-      <x:c r="A218" s="0" t="s">
-        <x:v>661</x:v>
-      </x:c>
-      <x:c r="B218" s="0" t="s">
-        <x:v>662</x:v>
-      </x:c>
-      <x:c r="C218" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D218" s="0" t="s">
-        <x:v>663</x:v>
-      </x:c>
-      <x:c r="E218" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G218" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="219" spans="1:7">
-      <x:c r="A219" s="0" t="s">
-        <x:v>664</x:v>
-      </x:c>
-      <x:c r="B219" s="0" t="s">
-        <x:v>665</x:v>
-      </x:c>
-      <x:c r="C219" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D219" s="0" t="s">
-        <x:v>666</x:v>
-      </x:c>
-      <x:c r="E219" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G219" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="220" spans="1:7">
-      <x:c r="A220" s="0" t="s">
-        <x:v>667</x:v>
-      </x:c>
-      <x:c r="B220" s="0" t="s">
-        <x:v>668</x:v>
-      </x:c>
-      <x:c r="C220" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D220" s="0" t="s">
-        <x:v>669</x:v>
-      </x:c>
-      <x:c r="E220" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G220" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="221" spans="1:7">
-      <x:c r="A221" s="0" t="s">
-        <x:v>670</x:v>
-      </x:c>
-      <x:c r="B221" s="0" t="s">
-        <x:v>671</x:v>
-      </x:c>
-      <x:c r="C221" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D221" s="0" t="s">
-        <x:v>672</x:v>
-      </x:c>
-      <x:c r="E221" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G221" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="222" spans="1:7">
-      <x:c r="A222" s="0" t="s">
-        <x:v>673</x:v>
-      </x:c>
-      <x:c r="B222" s="0" t="s">
-        <x:v>674</x:v>
-      </x:c>
-      <x:c r="C222" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D222" s="0" t="s">
-        <x:v>675</x:v>
-      </x:c>
-      <x:c r="E222" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G222" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="223" spans="1:7">
-      <x:c r="A223" s="0" t="s">
-        <x:v>676</x:v>
-      </x:c>
-      <x:c r="B223" s="0" t="s">
-        <x:v>677</x:v>
-      </x:c>
-      <x:c r="C223" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D223" s="0" t="s">
-        <x:v>678</x:v>
-      </x:c>
-      <x:c r="E223" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G223" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="224" spans="1:7">
-      <x:c r="A224" s="0" t="s">
-        <x:v>679</x:v>
-      </x:c>
-      <x:c r="B224" s="0" t="s">
-        <x:v>680</x:v>
-      </x:c>
-      <x:c r="C224" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D224" s="0" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="E224" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G224" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="225" spans="1:7">
-      <x:c r="A225" s="0" t="s">
-        <x:v>682</x:v>
-      </x:c>
-      <x:c r="B225" s="0" t="s">
-        <x:v>683</x:v>
-      </x:c>
-      <x:c r="C225" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D225" s="0" t="s">
-        <x:v>684</x:v>
-      </x:c>
-      <x:c r="E225" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G225" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -7203,7 +5707,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0100-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>

--- a/Data/LREROBOT/Rapport.xlsx
+++ b/Data/LREROBOT/Rapport.xlsx
@@ -49,1633 +49,1561 @@
     <x:t>Sous Dossier</x:t>
   </x:si>
   <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\_980 0033 67074 B 01 .pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115649_MATMUTRPA_000000001.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fail</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE011 -Extraction KO/format KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Non</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115653_MATMUTRPA_000000002.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115659_MATMUTRPA_000000003.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115700_MATMUTRPA_000000004.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115700_MATMUTRPA_000000005.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115701_MATMUTRPA_000000006.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115702_MATMUTRPA_000000007.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115702_MATMUTRPA_000000008.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115703_MATMUTRPA_000000009.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-0b7627d7-1d6c-48dc-a965-1603668c1f7e-6eca2e86d4b64bfa97c93d76258c490b.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115704_MATMUTRPA_000000011.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-1d9a65fc-32da-4966-be02-6b245853558d-b157206dacea4b17ab283f53537ab3e1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115705_MATMUTRPA_000000012.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-261d2106-86b9-4286-b8a0-f541dee4c1ff-8c2abf9cbf8b4db1bcd12869c630e227.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115705_MATMUTRPA_000000013.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-2e4acd3c-dcac-4447-a896-9788960fc9df-fb64965082e642cc903dfdb7c2a2b7e9.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115706_MATMUTRPA_000000014.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-34b69bf6-22b6-442f-99dc-4d540821382f-c3f8f010af6442e08314016013b3943c.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115707_MATMUTRPA_000000015.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-41caba1f-9585-4ad9-bc8c-2b61ddb11ba8-b80fd010cd3f4434a24f2ca9a13388cc.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115708_MATMUTRPA_000000016.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-538222e7-c391-4f5c-98f0-6094bc3e36e3-ae680ebeafa5462b9cbcf0c9ef369277.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115708_MATMUTRPA_000000017.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-5adf900c-5bbd-489c-8f17-3203c28bceb4-499f2e67f9f941149c4134b435eb568b.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115709_MATMUTRPA_000000018.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-60254d47-6f17-48b4-bcc8-3ad2476c97db-57c26eeaf22243469a754ad823ae05e3.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115710_MATMUTRPA_000000019.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-72905918-5d9e-4902-a217-3b3578d318ee-d53f87443b474ce696c632ba10cd01f1.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115711_MATMUTRPA_000000020.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-9e7f26ff-6a64-42ed-a3f4-6d4d1927ecc0-2d3294623f924ec4ab82ce1a20b8ca3f.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115713_MATMUTRPA_000000021.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-a7a283b3-12ed-461f-a410-da38109fe432-b5cf3950094b49e7aa6654cd5b505c97.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115713_MATMUTRPA_000000022.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-b9e9838b-54f3-490f-8706-ab0cecfd4a8d-70c4b9c25e01420f9eccbf4cb349d568.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115714_MATMUTRPA_000000023.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-bc75719f-0e52-43a6-8953-6f0ef0959427-df70e4692e5b4f6c82f965461fc63970.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115715_MATMUTRPA_000000024.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE014 - [800370709095F | la clé extraite F   est différente de la clé générée Z] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-d7b5dbf5-25c6-4131-9f4d-1d6e0c2fa058-d473d2a755dc43bba591baaca70ff1bb.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115716_MATMUTRPA_000000025.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-f0fdaf5b-420d-469a-a394-3b9e9993da20-82cbc868c06f4965bdf49cdb776af571.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115716_MATMUTRPA_000000026.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-fbedc888-178a-4175-8126-629b4883f304-82c7244800fe4ebea415e06ea86af128.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115717_MATMUTRPA_000000027.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150241_MATMUTRPA_000000001.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115717_MATMUTRPA_000000028.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE012 - [Santé] Hors périmètre</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150305_MATMUTRPA_000000003.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115718_MATMUTRPA_000000029.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150311_MATMUTRPA_000000009.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115719_MATMUTRPA_000000030.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150314_MATMUTRPA_000000014.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115720_MATMUTRPA_000000031.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150316_MATMUTRPA_000000016.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115721_MATMUTRPA_000000032.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250805_133800_MATMUTRPA_000000001.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115722_MATMUTRPA_000000033.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE012 - 980000162834MTC| Hors périmètre</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250828_093211_MATMUTRPA_000000081.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115723_MATMUTRPA_000000034.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250828_093255_MATMUTRPA_000000134.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115724_MATMUTRPA_000000035.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250828_143138_MATMUTRPA_000000047.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115725_MATMUTRPA_000000036.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115726_MATMUTRPA_000000037.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\28284-12900402-NOTIF-2024-11-22-13100402-461b2d82-cec6-422e-9477-92fe7c106dbe-a4b2eb3440a240538dc2c7c9dab6d27f.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115726_MATMUTRPA_000000038.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\28284-12900402-NOTIF-2024-11-22-13100402-be8b2fde-eaa7-4fef-9c86-f9cf394a9158-f05448874c204e8f97c5021cace221e9.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115727_MATMUTRPA_000000039.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\40763-04550404-NOTIF-2024-11-22-13100402-17c8e4dd-5ea3-4b7d-b981-ce1fc8701fe5-626f4115dcfd47e5bb8684b4302becbc.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115728_MATMUTRPA_000000040.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\40763-04550404-NOTIF-2024-11-22-13100402-398ccc85-4870-4ac2-a681-2341e8942eec-acdc01e31a644e0897669be1340a2bed.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115728_MATMUTRPA_000000041.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-10-07T105607.700.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115729_MATMUTRPA_000000042.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-10-07T110627.030.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115730_MATMUTRPA_000000043.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T135427.629.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115731_MATMUTRPA_000000044.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T135602.938.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115731_MATMUTRPA_000000045.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T135729.486.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115732_MATMUTRPA_000000046.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140113.150.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115733_MATMUTRPA_000000047.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140229.156.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115734_MATMUTRPA_000000048.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140312.416.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115735_MATMUTRPA_000000049.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140407.802.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115735_MATMUTRPA_000000050.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140503.945.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115736_MATMUTRPA_000000051.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140554.081.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115737_MATMUTRPA_000000052.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140635.034.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115738_MATMUTRPA_000000053.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140722.293.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115738_MATMUTRPA_000000054.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140820.205.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115739_MATMUTRPA_000000055.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140909.695.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115740_MATMUTRPA_000000056.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140949.978.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115740_MATMUTRPA_000000057.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141038.018.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115741_MATMUTRPA_000000058.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141117.536.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115742_MATMUTRPA_000000059.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141207.446.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115742_MATMUTRPA_000000060.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141322.570.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115743_MATMUTRPA_000000061.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141417.553.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115744_MATMUTRPA_000000062.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141514.019.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115744_MATMUTRPA_000000063.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\dossier inexistant - clef soc KO - 2.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115745_MATMUTRPA_000000064.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE014 - [240002548934U | la clé extraite U   est différente de la clé générée R] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\dossier inexistant - clef soc KO.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144248_MATMUTRPA_000000001.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fail</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [120000492449K | la clé extraite K   est différente de la clé générée Q] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Non</x:t>
+    <x:t>20250902_115746_MATMUTRPA_000000065.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE014 - [120000492449K | la clé extraite K   est différente de la clé générée C] BE014 - Clé num soc KO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\2337503928</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115747_MATMUTRPA_000000066.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Oui</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\4160914792</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115747_MATMUTRPA_000000067.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\1732366193</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115748_MATMUTRPA_000000068.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\2281907752</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115750_MATMUTRPA_000000069.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\2095807535</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115751_MATMUTRPA_000000070.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\3332348086</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115754_MATMUTRPA_000000071.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\2037793408</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115755_MATMUTRPA_000000072.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\7766679772</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144255_MATMUTRPA_000000002.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [840509002599L | la clé extraite L   est différente de la clé générée Y] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Oui</x:t>
+    <x:t>20250902_115756_MATMUTRPA_000000073.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\1009512117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115757_MATMUTRPA_000000074.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\6544809077</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115757_MATMUTRPA_000000075.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\3045825747</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115758_MATMUTRPA_000000076.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\6364486263</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115759_MATMUTRPA_000000077.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\6876400847</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115801_MATMUTRPA_000000078.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\9432160377</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144256_MATMUTRPA_000000003.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980000809205Y | la clé extraite Y   est différente de la clé générée C] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115802_MATMUTRPA_000000079.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\1879992102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115803_MATMUTRPA_000000080.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\5988929419</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115803_MATMUTRPA_000000081.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\9016932803</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144257_MATMUTRPA_000000004.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002669133E | la clé extraite E   est différente de la clé générée J] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144259_MATMUTRPA_000000005.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980001601482V | la clé extraite V   est différente de la clé générée H] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144300_MATMUTRPA_000000005.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980000996047P | la clé extraite P   est différente de la clé générée T] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002231588C | la clé extraite C   est différente de la clé générée A] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144301_MATMUTRPA_000000005.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002319455U | la clé extraite U   est différente de la clé générée G] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [500204000580R | la clé extraite R   est différente de la clé générée V] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144302_MATMUTRPA_000000005.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002584346K | la clé extraite K   est différente de la clé générée X] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE012 - [Santé] Hors périmètre</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002867805b | la clé extraite b   est différente de la clé générée P] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-0b7627d7-1d6c-48dc-a965-1603668c1f7e-6eca2e86d4b64bfa97c93d76258c490b.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144303_MATMUTRPA_000000006.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-2e4acd3c-dcac-4447-a896-9788960fc9df-fb64965082e642cc903dfdb7c2a2b7e9.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144304_MATMUTRPA_000000007.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-5adf900c-5bbd-489c-8f17-3203c28bceb4-499f2e67f9f941149c4134b435eb568b.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144304_MATMUTRPA_000000008.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250805_133800_MATMUTRPA_000000001.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144305_MATMUTRPA_000000009.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980000162834M | la clé extraite M   est différente de la clé générée Z] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\dossier inexistant - clef soc KO - 2.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144306_MATMUTRPA_000000010.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [240002548934U | la clé extraite U   est différente de la clé générée V] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-261d2106-86b9-4286-b8a0-f541dee4c1ff-8c2abf9cbf8b4db1bcd12869c630e227.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144306_MATMUTRPA_000000011.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003668206N | la clé extraite N   est différente de la clé générée S] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-34b69bf6-22b6-442f-99dc-4d540821382f-c3f8f010af6442e08314016013b3943c.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144307_MATMUTRPA_000000012.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-41caba1f-9585-4ad9-bc8c-2b61ddb11ba8-b80fd010cd3f4434a24f2ca9a13388cc.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144308_MATMUTRPA_000000013.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-538222e7-c391-4f5c-98f0-6094bc3e36e3-ae680ebeafa5462b9cbcf0c9ef369277.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144308_MATMUTRPA_000000014.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [960001101990Q | la clé extraite Q   est différente de la clé générée U] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-60254d47-6f17-48b4-bcc8-3ad2476c97db-57c26eeaf22243469a754ad823ae05e3.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144309_MATMUTRPA_000000015.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [830409004820P | la clé extraite P   est différente de la clé générée T] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-72905918-5d9e-4902-a217-3b3578d318ee-d53f87443b474ce696c632ba10cd01f1.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144310_MATMUTRPA_000000016.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-9e7f26ff-6a64-42ed-a3f4-6d4d1927ecc0-2d3294623f924ec4ab82ce1a20b8ca3f.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144310_MATMUTRPA_000000017.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-a7a283b3-12ed-461f-a410-da38109fe432-b5cf3950094b49e7aa6654cd5b505c97.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144311_MATMUTRPA_000000018.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE011 -Extraction KO/format KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-b9e9838b-54f3-490f-8706-ab0cecfd4a8d-70c4b9c25e01420f9eccbf4cb349d568.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144312_MATMUTRPA_000000019.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980000802716M | la clé extraite M   est différente de la clé générée Z] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-bc75719f-0e52-43a6-8953-6f0ef0959427-df70e4692e5b4f6c82f965461fc63970.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144312_MATMUTRPA_000000020.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [800370709095F | la clé extraite F   est différente de la clé générée D] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-d7b5dbf5-25c6-4131-9f4d-1d6e0c2fa058-d473d2a755dc43bba591baaca70ff1bb.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144313_MATMUTRPA_000000021.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002691729L | la clé extraite L   est différente de la clé générée Y] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-f0fdaf5b-420d-469a-a394-3b9e9993da20-82cbc868c06f4965bdf49cdb776af571.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144314_MATMUTRPA_000000022.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [740109006318S | la clé extraite S   est différente de la clé générée E] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\14596-11380402-NOTIF-2024-11-22-13100402-fbedc888-178a-4175-8126-629b4883f304-82c7244800fe4ebea415e06ea86af128.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144314_MATMUTRPA_000000023.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [450209002215X | la clé extraite X   est différente de la clé générée B] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150241_MATMUTRPA_000000001.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144315_MATMUTRPA_000000024.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150305_MATMUTRPA_000000003.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144316_MATMUTRPA_000000025.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150311_MATMUTRPA_000000009.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144317_MATMUTRPA_000000026.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150314_MATMUTRPA_000000014.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144318_MATMUTRPA_000000027.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\20250804_150316_MATMUTRPA_000000016.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144318_MATMUTRPA_000000028.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\28284-12900402-NOTIF-2024-11-22-13100402-461b2d82-cec6-422e-9477-92fe7c106dbe-a4b2eb3440a240538dc2c7c9dab6d27f.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144319_MATMUTRPA_000000029.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\28284-12900402-NOTIF-2024-11-22-13100402-be8b2fde-eaa7-4fef-9c86-f9cf394a9158-f05448874c204e8f97c5021cace221e9.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144320_MATMUTRPA_000000030.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002163671G | la clé extraite G   est différente de la clé générée L] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\40763-04550404-NOTIF-2024-11-22-13100402-17c8e4dd-5ea3-4b7d-b981-ce1fc8701fe5-626f4115dcfd47e5bb8684b4302becbc.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144321_MATMUTRPA_000000031.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980001360786F | la clé extraite F   est différente de la clé générée K] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\40763-04550404-NOTIF-2024-11-22-13100402-398ccc85-4870-4ac2-a681-2341e8942eec-acdc01e31a644e0897669be1340a2bed.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144321_MATMUTRPA_000000032.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003284391H | la clé extraite H   est différente de la clé générée M] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T135427.629.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144322_MATMUTRPA_000000033.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [960000651112N | la clé extraite N   est différente de la clé générée S] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T135602.938.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144323_MATMUTRPA_000000034.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [759100003262F | la clé extraite F   est différente de la clé générée K] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T135729.486.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144323_MATMUTRPA_000000035.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002699086A | la clé extraite A   est différente de la clé générée P] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140113.150.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144324_MATMUTRPA_000000036.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980000549752F | la clé extraite F   est différente de la clé générée K] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140229.156.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144325_MATMUTRPA_000000037.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003532138D | la clé extraite D   est différente de la clé générée R] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140312.416.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144326_MATMUTRPA_000000038.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002834151M | la clé extraite M   est différente de la clé générée Z] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140407.802.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144327_MATMUTRPA_000000039.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002570501k | la clé extraite k   est différente de la clé générée X] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140503.945.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144327_MATMUTRPA_000000040.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002286686F | la clé extraite F   est différente de la clé générée K] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140554.081.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144328_MATMUTRPA_000000041.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980001956663G | la clé extraite G   est différente de la clé générée L] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140635.034.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144329_MATMUTRPA_000000042.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002409304J | la clé extraite J   est différente de la clé générée W] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140722.293.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144330_MATMUTRPA_000000043.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140820.205.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144330_MATMUTRPA_000000044.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002022787B | la clé extraite B   est différente de la clé générée D] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140909.695.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144331_MATMUTRPA_000000045.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [570109000951N | la clé extraite N   est différente de la clé générée S] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T140949.978.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144332_MATMUTRPA_000000046.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003174468T | la clé extraite T   est différente de la clé générée F] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141038.018.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144332_MATMUTRPA_000000047.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003511683Y | la clé extraite Y   est différente de la clé générée C] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141117.536.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144333_MATMUTRPA_000000048.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141207.446.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144334_MATMUTRPA_000000049.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002449095N | la clé extraite N   est différente de la clé générée S] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141322.570.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144334_MATMUTRPA_000000050.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003185070B | la clé extraite B   est différente de la clé générée D] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141417.553.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144335_MATMUTRPA_000000051.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>51</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002921162W | la clé extraite W   est différente de la clé générée A] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\Demande de resiliation Hamon - 2024-11-25T141514.019.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144336_MATMUTRPA_000000052.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980000628327V | la clé extraite V   est différente de la clé générée H] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\1732366193</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144336_MATMUTRPA_000000053.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003891334Z | la clé extraite Z   est différente de la clé générée D] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\2281907752</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144337_MATMUTRPA_000000054.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003177319U | la clé extraite U   est différente de la clé générée G] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\2095807535</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144338_MATMUTRPA_000000055.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980000864226P | la clé extraite P   est différente de la clé générée T] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\3332348086</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144339_MATMUTRPA_000000056.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\2037793408</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144340_MATMUTRPA_000000057.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002014599R | la clé extraite R   est différente de la clé générée V] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\1009512117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144341_MATMUTRPA_000000058.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002293007G | la clé extraite G   est différente de la clé générée L] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\6544809077</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144341_MATMUTRPA_000000059.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [510709001741F | la clé extraite F   est différente de la clé générée K] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\3045825747</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144342_MATMUTRPA_000000060.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\6364486263</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144343_MATMUTRPA_000000061.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980000535994X | la clé extraite X   est différente de la clé générée B] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\6876400847</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144344_MATMUTRPA_000000062.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\1879992102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144345_MATMUTRPA_000000063.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002584766V | la clé extraite V   est différente de la clé générée H] BE014 - Clé num soc KO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C:\DATA\LRE RES\Fichier d'entrée\5988929419</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20250813_144345_MATMUTRPA_000000064.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003084341H | la clé extraite H   est différente de la clé générée M] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115805_MATMUTRPA_000000082.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>82</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\message_43310327_resiliation@matmut.fr.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144346_MATMUTRPA_000000065.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>65</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002057643U | la clé extraite U   est différente de la clé générée G] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115806_MATMUTRPA_000000083.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\message_43310334_resiliation@matmut.fr.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144347_MATMUTRPA_000000066.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980900224297k | la clé extraite k   est différente de la clé générée X] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115806_MATMUTRPA_000000084.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>84</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\message_43310361_resiliation@matmut.fr.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144348_MATMUTRPA_000000067.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980000771436D | la clé extraite D   est différente de la clé générée R] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115807_MATMUTRPA_000000085.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\message_43310674_resiliation@matmut.fr.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144349_MATMUTRPA_000000068.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002150415V | la clé extraite V   est différente de la clé générée H] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115808_MATMUTRPA_000000086.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\message_43335289_resiliation@matmut.fr.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144349_MATMUTRPA_000000069.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002484576Y | la clé extraite Y   est différente de la clé générée C] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115809_MATMUTRPA_000000087.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\message_43379712_resiliation@matmut.fr.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144350_MATMUTRPA_000000070.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002049129S | la clé extraite S   est différente de la clé générée E] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115810_MATMUTRPA_000000088.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>88</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\message_43425700_resiliation@matmut.fr.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144351_MATMUTRPA_000000071.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003306188Q | la clé extraite Q   est différente de la clé générée U] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115811_MATMUTRPA_000000089.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-873846be-1a72-46f8-99b1-96a162f0e422.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144351_MATMUTRPA_000000072.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [750209007074H | la clé extraite H   est différente de la clé générée M] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115811_MATMUTRPA_000000090.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-a4d7dc50-1859-42d5-8719-089e9b9dde71.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144352_MATMUTRPA_000000073.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [960000068849A | la clé extraite A   est différente de la clé générée P] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115812_MATMUTRPA_000000091.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-a87518f5-6477-42a0-bebc-18c0f42df781.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144355_MATMUTRPA_000000074.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [560104002270X | la clé extraite X   est différente de la clé générée B] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115814_MATMUTRPA_000000092.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-ba00efcc-5cf9-4fef-84f4-2014e001ec49.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144357_MATMUTRPA_000000075.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003033071M | la clé extraite M   est différente de la clé générée Z] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115815_MATMUTRPA_000000093.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-cbb3e6bc-cf3e-4aa1-bc80-7e48c234e478.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144357_MATMUTRPA_000000076.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980001503958D | la clé extraite D   est différente de la clé générée R] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115816_MATMUTRPA_000000094.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-d81d8a6b-1e4c-4e63-b367-d9b8886c6d9a.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144358_MATMUTRPA_000000077.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>77</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980000661440V | la clé extraite V   est différente de la clé générée H] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115816_MATMUTRPA_000000095.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-d8d535d2-0678-41f4-815f-04dff1d2dd0c.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144359_MATMUTRPA_000000078.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002931617H | la clé extraite H   est différente de la clé générée M] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115817_MATMUTRPA_000000096.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>96</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-dca5a1ab-31e9-47b8-8c86-d8e5f682607e.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144400_MATMUTRPA_000000079.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [960001328099R | la clé extraite R   est différente de la clé générée V] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115818_MATMUTRPA_000000097.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-e4947664-09fe-4856-91fa-a54ffced7ee6.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144401_MATMUTRPA_000000080.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>80</x:t>
+    <x:t>20250902_115819_MATMUTRPA_000000098.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-e55206cb-5ecf-4568-9183-a280a60e41c1.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144401_MATMUTRPA_000000081.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81</x:t>
+    <x:t>20250902_115820_MATMUTRPA_000000099.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-eeb82fcb-dfb1-4b9a-9bff-e411581472ce.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144402_MATMUTRPA_000000082.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [352011314457M | la clé extraite M   est différente de la clé générée Z] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115820_MATMUTRPA_000000100.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_600-f301cec9-984a-450e-b224-c563f5203433.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144403_MATMUTRPA_000000083.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980900006190E | la clé extraite E   est différente de la clé générée J] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115821_MATMUTRPA_000000101.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>101</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-02e06e81-c885-431d-a456-60ab127dc071.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144404_MATMUTRPA_000000084.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>84</x:t>
+    <x:t>20250902_115822_MATMUTRPA_000000102.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>102</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-0e0aea93-f361-4739-9ed7-cdb67803fd84.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144405_MATMUTRPA_000000085.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85</x:t>
+    <x:t>20250902_115823_MATMUTRPA_000000103.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>103</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-1715cf71-724d-45b6-8e15-e86c557419a4.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144406_MATMUTRPA_000000086.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>86</x:t>
+    <x:t>20250902_115823_MATMUTRPA_000000104.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>104</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-1876f30c-83a4-4a4c-9c55-094fdf3ac844.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144406_MATMUTRPA_000000087.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>87</x:t>
+    <x:t>20250902_115824_MATMUTRPA_000000105.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>105</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-19c03249-bbfc-4c49-b058-3af16c158f0f.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144407_MATMUTRPA_000000088.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>88</x:t>
+    <x:t>20250902_115825_MATMUTRPA_000000106.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>106</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-1aeb8441-3356-4a2d-ba7c-d783f27dae69.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144408_MATMUTRPA_000000089.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89</x:t>
+    <x:t>20250902_115826_MATMUTRPA_000000107.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>107</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-1c7cbc6f-6bb2-4b7b-9968-ca6bc78fe996.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144409_MATMUTRPA_000000090.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90</x:t>
+    <x:t>20250902_115826_MATMUTRPA_000000108.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>108</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-23557855-7620-4ae5-9241-fcc4412132a8.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144409_MATMUTRPA_000000091.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003104385B | la clé extraite B   est différente de la clé générée D] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115827_MATMUTRPA_000000109.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>109</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-23e9ee7b-1c83-4124-9a3b-1f8b9052a987.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144410_MATMUTRPA_000000092.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>92</x:t>
+    <x:t>20250902_115828_MATMUTRPA_000000110.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>110</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-338f2191-3f8d-4d87-9910-2483cf9753d1.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144411_MATMUTRPA_000000093.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93</x:t>
+    <x:t>20250902_115829_MATMUTRPA_000000111.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>111</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-38ca5ea7-46a9-422d-a449-10947af6f55a.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144412_MATMUTRPA_000000094.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>94</x:t>
+    <x:t>20250902_115830_MATMUTRPA_000000112.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>112</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-3c267d7a-d52b-4492-a732-7a3e45159f79.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144412_MATMUTRPA_000000095.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95</x:t>
+    <x:t>20250902_115831_MATMUTRPA_000000113.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>113</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-3df6b24f-3c10-49d2-bef4-85d02d4d32c8.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144413_MATMUTRPA_000000096.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>96</x:t>
+    <x:t>20250902_115832_MATMUTRPA_000000114.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>114</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-40f6d100-df71-4cb6-b435-c92ee1b7a806.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144414_MATMUTRPA_000000097.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>97</x:t>
+    <x:t>20250902_115833_MATMUTRPA_000000115.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>115</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-43115be2-cca2-44d8-bb9c-2abec01bff83.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144414_MATMUTRPA_000000098.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>98</x:t>
+    <x:t>20250902_115834_MATMUTRPA_000000116.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>116</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-4ac8d681-6792-426f-a1d9-97439fdd85b0.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144415_MATMUTRPA_000000099.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99</x:t>
+    <x:t>20250902_115835_MATMUTRPA_000000117.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>117</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-4f14000d-93a1-4515-80d8-b2647251b2e4.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144416_MATMUTRPA_000000100.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100</x:t>
+    <x:t>20250902_115835_MATMUTRPA_000000118.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>118</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-50842b6b-c5bf-4c18-bc16-877c4c658790.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144417_MATMUTRPA_000000101.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>101</x:t>
+    <x:t>20250902_115836_MATMUTRPA_000000119.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>119</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-511d976d-b673-4616-b1d9-9e81134c4b9a.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144417_MATMUTRPA_000000102.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>102</x:t>
+    <x:t>20250902_115837_MATMUTRPA_000000120.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>120</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-5dd7dfad-d899-4d3b-a948-16f50763249c.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144418_MATMUTRPA_000000103.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>103</x:t>
+    <x:t>20250902_115838_MATMUTRPA_000000121.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>121</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-5dee5d56-af0d-46cb-bacc-b7045d169bf1.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144419_MATMUTRPA_000000104.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>104</x:t>
+    <x:t>20250902_115839_MATMUTRPA_000000122.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>122</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-5effc335-5e66-4e89-b745-0ceb6dc2c5c5.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144419_MATMUTRPA_000000105.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>105</x:t>
+    <x:t>20250902_115840_MATMUTRPA_000000123.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-639a98d2-4d8b-435f-8ce8-5a057d8b78c1.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144420_MATMUTRPA_000000106.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>106</x:t>
+    <x:t>20250902_115841_MATMUTRPA_000000124.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>124</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-6704a614-5d1d-45b6-baba-c9cec9602725.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144421_MATMUTRPA_000000107.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>107</x:t>
+    <x:t>20250902_115842_MATMUTRPA_000000125.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>125</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-6e8fb98b-af36-48fc-8783-522c7503abf0.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144422_MATMUTRPA_000000108.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>108</x:t>
+    <x:t>20250902_115843_MATMUTRPA_000000126.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>126</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-862c1b42-9ca9-4924-90b0-2add3d55dac1.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144422_MATMUTRPA_000000109.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>109</x:t>
+    <x:t>20250902_115844_MATMUTRPA_000000127.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>127</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-87eb1dd7-d4f7-4fc7-844f-30c91916f02e.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144423_MATMUTRPA_000000110.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>110</x:t>
+    <x:t>20250902_115845_MATMUTRPA_000000128.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>128</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-8b93f0c7-0ce0-4043-9076-2f4ead2f6138.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144424_MATMUTRPA_000000111.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>111</x:t>
+    <x:t>20250902_115845_MATMUTRPA_000000129.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>129</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-9347e787-ae92-415a-a649-74f85e64cadc.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144424_MATMUTRPA_000000112.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>112</x:t>
+    <x:t>20250902_115846_MATMUTRPA_000000130.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>130</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-9c432c50-7279-4cd1-af92-6731fbf41cd7.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144425_MATMUTRPA_000000113.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>113</x:t>
+    <x:t>20250902_115847_MATMUTRPA_000000131.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>131</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-9c98cb9f-999e-4847-a360-b1b442ff7fb2.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144426_MATMUTRPA_000000114.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>114</x:t>
+    <x:t>20250902_115849_MATMUTRPA_000000132.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>132</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-9f675ec0-f692-481f-ab22-339db6b5c823.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144427_MATMUTRPA_000000115.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>115</x:t>
+    <x:t>20250902_115849_MATMUTRPA_000000133.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>133</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-ab2cdf1d-96cc-40f7-a5d1-2eed4bb8c1a8.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144427_MATMUTRPA_000000116.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>116</x:t>
+    <x:t>20250902_115850_MATMUTRPA_000000134.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>134</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-b14c24a0-df7f-4867-9af7-7684384f7cf4.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144428_MATMUTRPA_000000117.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>117</x:t>
+    <x:t>20250902_115851_MATMUTRPA_000000135.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>135</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-b1acac80-cd9a-404f-9b5c-1f12c4f0b3d1.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144429_MATMUTRPA_000000118.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>118</x:t>
+    <x:t>20250902_115853_MATMUTRPA_000000136.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>136</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-b5f51aef-7f38-4d58-95c3-5d21eb9d3e8f.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144429_MATMUTRPA_000000119.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>119</x:t>
+    <x:t>20250902_115853_MATMUTRPA_000000137.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>137</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-b8b50afc-4c0b-4baa-ad53-0da3585df128.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144430_MATMUTRPA_000000120.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>120</x:t>
+    <x:t>20250902_115854_MATMUTRPA_000000138.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>138</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-c2f71dca-64b8-44d6-a5b6-88dc1e338034.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144431_MATMUTRPA_000000121.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>121</x:t>
+    <x:t>20250902_115855_MATMUTRPA_000000139.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>139</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-c544fba4-fd1a-478c-b5fe-ad7a98d83837.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144431_MATMUTRPA_000000122.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>122</x:t>
+    <x:t>20250902_115856_MATMUTRPA_000000140.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>140</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-c76eeee5-6d36-453a-8263-c16fd1da92c8.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144432_MATMUTRPA_000000123.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123</x:t>
+    <x:t>20250902_115856_MATMUTRPA_000000141.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>141</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-caef8afe-5917-4618-b8c7-4e3da45467d3.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144433_MATMUTRPA_000000124.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>124</x:t>
+    <x:t>20250902_115857_MATMUTRPA_000000142.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>142</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-cf45e6ae-3326-4774-8b4c-649c088cc2d1.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144433_MATMUTRPA_000000125.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>125</x:t>
+    <x:t>20250902_115858_MATMUTRPA_000000143.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>143</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-da489881-d2e3-4ef1-9711-2611be3b4090.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144434_MATMUTRPA_000000126.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>126</x:t>
+    <x:t>20250902_115859_MATMUTRPA_000000144.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-e4af891b-489e-41f8-91e3-231ab61cf5b1.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144435_MATMUTRPA_000000127.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>127</x:t>
+    <x:t>20250902_115900_MATMUTRPA_000000145.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>145</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-ec450215-2d71-492b-a8fc-5cfbf3eefff8.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144436_MATMUTRPA_000000128.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>128</x:t>
+    <x:t>20250902_115901_MATMUTRPA_000000146.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>146</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-edbc96f1-f7f3-4d49-8289-c5d79161b984.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144436_MATMUTRPA_000000129.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>129</x:t>
+    <x:t>20250902_115902_MATMUTRPA_000000147.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>147</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-fde41c47-c3ec-433a-85d4-ba6300678a48.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144437_MATMUTRPA_000000130.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>130</x:t>
+    <x:t>20250902_115903_MATMUTRPA_000000148.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>148</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-fea503bc-7ab5-4676-9a12-0037e9b64197.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144438_MATMUTRPA_000000131.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>131</x:t>
+    <x:t>20250902_115904_MATMUTRPA_000000149.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>149</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-ff89c62b-722a-4e3c-a633-02d8ae58d348.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144438_MATMUTRPA_000000132.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>132</x:t>
+    <x:t>20250902_115904_MATMUTRPA_000000150.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>150</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_700-ffe34624-db37-4b42-9319-c6fa38769538.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144439_MATMUTRPA_000000133.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>133</x:t>
+    <x:t>20250902_115905_MATMUTRPA_000000151.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>151</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-030f5bfd-1113-4138-9749-c114a871e88c.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144440_MATMUTRPA_000000134.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>134</x:t>
+    <x:t>20250902_115906_MATMUTRPA_000000152.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE014 - [980002111058Z | la clé extraite Z   est différente de la clé générée U] BE014 - Clé num soc KO</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-0d8bcc33-75ee-4717-ab8c-9c317ac942aa.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144440_MATMUTRPA_000000135.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [200209005929Q | la clé extraite Q   est différente de la clé générée U] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115907_MATMUTRPA_000000153.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>153</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-4269d6d1-341d-4cbc-a71e-d00aa13f0fdd.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144441_MATMUTRPA_000000136.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>136</x:t>
+    <x:t>20250902_115908_MATMUTRPA_000000154.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>154</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-4add1608-3e4b-4bde-9bf4-fb1635da3518.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144442_MATMUTRPA_000000137.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>137</x:t>
+    <x:t>20250902_115908_MATMUTRPA_000000155.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>155</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-4b81cdd8-ed5d-4642-9774-a0991aab605a.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144442_MATMUTRPA_000000138.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>138</x:t>
+    <x:t>20250902_115909_MATMUTRPA_000000156.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>156</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-4ffbf570-f356-4ad7-8dc2-3bbe887ea42f.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144443_MATMUTRPA_000000139.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>139</x:t>
+    <x:t>20250902_115910_MATMUTRPA_000000157.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>157</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-6635e8e7-7bbe-47ec-8d0f-e3ae14e1d08a.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144444_MATMUTRPA_000000140.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>140</x:t>
+    <x:t>20250902_115911_MATMUTRPA_000000158.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>158</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-6f57bddf-4c41-46aa-b7cf-7a4a61152ff2.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144445_MATMUTRPA_000000141.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>141</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [941100007093n | la clé extraite n   est différente de la clé générée S] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115911_MATMUTRPA_000000159.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>159</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-75efcddd-7b66-4b08-96b3-7f163f37a5d2.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144445_MATMUTRPA_000000142.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>142</x:t>
+    <x:t>20250902_115912_MATMUTRPA_000000160.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>160</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-818e18bb-5359-4e2e-a365-ca5dcc2ba43e.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144446_MATMUTRPA_000000143.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>143</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980000790056R | la clé extraite R   est différente de la clé générée V] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115913_MATMUTRPA_000000161.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>161</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-951d5cc1-89f3-4898-aa04-b7ef3f640038.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144447_MATMUTRPA_000000144.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>144</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003071043N | la clé extraite N   est différente de la clé générée S] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115915_MATMUTRPA_000000162.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>162</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-9562fdc3-ce0b-47e5-be2e-57d90ef0b482.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144447_MATMUTRPA_000000145.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>145</x:t>
+    <x:t>20250902_115916_MATMUTRPA_000000163.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>163</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-986b17de-a3f8-4439-9056-eb5a9b081769.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144448_MATMUTRPA_000000146.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003236201D | la clé extraite D   est différente de la clé générée R] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115916_MATMUTRPA_000000164.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>164</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-a223cb74-6dd5-41ac-9080-f8896cb4fd91.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144449_MATMUTRPA_000000147.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>147</x:t>
+    <x:t>20250902_115917_MATMUTRPA_000000165.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>165</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-c253907c-e75f-48e1-95bb-f17e815b7d9e.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144450_MATMUTRPA_000000148.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003776917Q | la clé extraite Q   est différente de la clé générée U] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115919_MATMUTRPA_000000166.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>166</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-da19c964-68bd-46ae-b867-c00319278874.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144451_MATMUTRPA_000000149.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980003544355Y | la clé extraite Y   est différente de la clé générée C] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115920_MATMUTRPA_000000167.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>167</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-dc219e73-57b8-476f-bf37-81013502ec86.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144451_MATMUTRPA_000000150.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [980002460150Y | la clé extraite Y   est différente de la clé générée C] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115920_MATMUTRPA_000000168.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>168</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-e767552f-bec9-4f74-a950-91b6e2d51a39.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144452_MATMUTRPA_000000151.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>151</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [139100002235P | la clé extraite P   est différente de la clé générée T] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115921_MATMUTRPA_000000169.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>169</x:t>
   </x:si>
   <x:si>
     <x:t>C:\DATA\LRE RES\Fichier d'entrée\tessi_777-f31075a6-6584-4298-b5c5-fb27b0d71eca.pdf</x:t>
   </x:si>
   <x:si>
-    <x:t>20250813_144453_MATMUTRPA_000000152.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BE014 - [170609001247S | la clé extraite S   est différente de la clé générée E] BE014 - Clé num soc KO</x:t>
+    <x:t>20250902_115923_MATMUTRPA_000000170.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>170</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\test 5.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115924_MATMUTRPA_000000171.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>171</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115924_MATMUTRPA_000000172.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C:\DATA\LRE RES\Fichier d'entrée\test6.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20250902_115926_MATMUTRPA_000000174.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BE017 -Le fichier PDF ne contient pas de texte (image)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2051,269 +1979,236 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
@@ -2330,13 +2225,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F14" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
@@ -2353,13 +2245,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
@@ -2376,13 +2265,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
@@ -2399,3302 +2285,3226 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B18" s="0" t="s">
+      <x:c r="C18" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F23" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F25" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F27" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F34" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F35" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F36" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F40" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F44" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F46" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F47" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F48" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F49" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F50" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F51" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F52" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F53" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F54" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F55" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F56" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G56" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F57" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G57" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F58" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G58" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F59" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G59" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F60" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G60" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F61" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G61" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F62" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G62" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F63" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G63" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G64" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G65" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G66" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G67" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F68" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G68" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F69" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G69" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F70" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G70" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F71" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G71" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F72" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G72" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F73" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G73" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F74" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G74" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F75" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G75" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G76" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F77" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G77" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G78" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F79" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G79" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F80" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G80" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F81" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G81" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F82" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G82" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F83" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G83" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F84" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G84" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F85" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G85" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F86" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G86" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F87" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G87" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F88" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G88" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F89" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G89" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F90" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G90" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F91" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G91" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F92" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G92" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F93" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G93" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F94" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G94" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F95" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G95" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F96" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G96" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F97" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G97" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F98" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G98" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F99" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G99" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F100" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G100" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F101" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G101" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F102" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G102" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G103" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F104" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G104" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F105" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G105" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G106" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G107" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F108" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G108" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F109" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G109" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F110" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G110" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F111" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G111" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F112" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G112" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F113" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G113" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:7">
       <x:c r="A114" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F114" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G114" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:7">
       <x:c r="A115" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G115" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7">
       <x:c r="A116" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F116" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G116" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:7">
       <x:c r="A117" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F117" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G117" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:7">
       <x:c r="A118" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F118" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G118" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:7">
       <x:c r="A119" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F119" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G119" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:7">
       <x:c r="A120" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F120" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G120" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:7">
       <x:c r="A121" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F121" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G121" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:7">
       <x:c r="A122" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G122" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:7">
       <x:c r="A123" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F123" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G123" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:7">
       <x:c r="A124" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F124" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G124" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:7">
       <x:c r="A125" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F125" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G125" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:7">
       <x:c r="A126" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F126" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G126" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:7">
       <x:c r="A127" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F127" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G127" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:7">
       <x:c r="A128" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G128" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:7">
       <x:c r="A129" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F129" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G129" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7">
       <x:c r="A130" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F130" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G130" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
       <x:c r="A131" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F131" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G131" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:7">
       <x:c r="A132" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F132" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G132" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:7">
       <x:c r="A133" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F133" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G133" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:7">
       <x:c r="A134" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F134" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G134" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:7">
       <x:c r="A135" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F135" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G135" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:7">
       <x:c r="A136" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G136" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:7">
       <x:c r="A137" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F137" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G137" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:7">
       <x:c r="A138" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F138" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G138" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:7">
       <x:c r="A139" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F139" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G139" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:7">
       <x:c r="A140" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F140" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G140" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:7">
       <x:c r="A141" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F141" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G141" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:7">
       <x:c r="A142" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F142" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G142" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:7">
       <x:c r="A143" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F143" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G143" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:7">
       <x:c r="A144" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F144" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G144" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:7">
       <x:c r="A145" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F145" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G145" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:7">
       <x:c r="A146" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F146" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G146" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:7">
       <x:c r="A147" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F147" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G147" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:7">
       <x:c r="A148" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G148" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:7">
       <x:c r="A149" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F149" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G149" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:7">
       <x:c r="A150" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F150" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G150" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:7">
       <x:c r="A151" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F151" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G151" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:7">
       <x:c r="A152" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="G152" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:7">
       <x:c r="A153" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F153" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G153" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:7">
       <x:c r="A154" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G154" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:7">
       <x:c r="A155" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G155" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:7">
       <x:c r="A156" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G156" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:7">
       <x:c r="A157" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F157" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G157" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:7">
       <x:c r="A158" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F158" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G158" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:7">
       <x:c r="A159" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F159" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G159" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:7">
       <x:c r="A160" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F160" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G160" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:7">
+      <x:c r="A161" s="0" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="E161" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G161" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:7">
+      <x:c r="A162" s="0" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D162" s="0" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="E162" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G162" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:7">
+      <x:c r="A163" s="0" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D163" s="0" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="E163" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G163" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:7">
+      <x:c r="A164" s="0" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D164" s="0" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="E164" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G164" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:7">
+      <x:c r="A165" s="0" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D165" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="E165" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G165" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:7">
+      <x:c r="A166" s="0" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D166" s="0" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="E166" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G166" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:7">
+      <x:c r="A167" s="0" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="E167" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G167" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:7">
+      <x:c r="A168" s="0" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="E168" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G168" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:7">
+      <x:c r="A169" s="0" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="E169" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G169" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:7">
+      <x:c r="A170" s="0" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="E170" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G170" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:7">
+      <x:c r="A171" s="0" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="C171" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F160" s="0" t="s">
-        <x:v>549</x:v>
-      </x:c>
-      <x:c r="G160" s="0" t="s">
-        <x:v>12</x:v>
+      <x:c r="D171" s="0" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="E171" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G171" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:7">
+      <x:c r="A172" s="0" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="E172" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G172" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:7">
+      <x:c r="A173" s="0" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="C173" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="E173" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F173" s="0" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="G173" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
